--- a/outputs/detailed-results/experiment_results_detailed.xlsx
+++ b/outputs/detailed-results/experiment_results_detailed.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf557ebc376424a56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主表" sheetId="1" r:id="Re68011103ed64d9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附录" sheetId="2" r:id="Rbca96f0b83444499"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -81,7 +82,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -104,6 +105,9 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -332,8 +336,6 @@
     <x:col min="20" max="20" width="9" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="9" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="9" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="9" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="9" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -348,45 +350,41 @@
       </x:c>
       <x:c r="D1" s="5"/>
       <x:c r="E1" s="5" t="str">
-        <x:v>EMAformer</x:v>
+        <x:v>DeepBooTS</x:v>
       </x:c>
       <x:c r="F1" s="5"/>
       <x:c r="G1" s="5" t="str">
-        <x:v>DeepBooTS</x:v>
+        <x:v>SimpleTM</x:v>
       </x:c>
       <x:c r="H1" s="5"/>
       <x:c r="I1" s="5" t="str">
-        <x:v>SimpleTM</x:v>
+        <x:v>FilterTS</x:v>
       </x:c>
       <x:c r="J1" s="5"/>
       <x:c r="K1" s="5" t="str">
-        <x:v>FilterTS</x:v>
+        <x:v>FACTS</x:v>
       </x:c>
       <x:c r="L1" s="5"/>
       <x:c r="M1" s="5" t="str">
-        <x:v>xPatch</x:v>
+        <x:v>iTransformer</x:v>
       </x:c>
       <x:c r="N1" s="5"/>
       <x:c r="O1" s="5" t="str">
-        <x:v>iTransformer</x:v>
+        <x:v>TimeMixer</x:v>
       </x:c>
       <x:c r="P1" s="5"/>
       <x:c r="Q1" s="5" t="str">
-        <x:v>TimeMixer</x:v>
+        <x:v>PatchTST</x:v>
       </x:c>
       <x:c r="R1" s="5"/>
       <x:c r="S1" s="5" t="str">
-        <x:v>PatchTST</x:v>
+        <x:v>TimesNet</x:v>
       </x:c>
       <x:c r="T1" s="5"/>
       <x:c r="U1" s="5" t="str">
-        <x:v>DLinear</x:v>
+        <x:v>FEDformer</x:v>
       </x:c>
       <x:c r="V1" s="5"/>
-      <x:c r="W1" s="5" t="str">
-        <x:v>FEDformer</x:v>
-      </x:c>
-      <x:c r="X1" s="5"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="5"/>
@@ -451,12 +449,6 @@
       <x:c r="V2" s="5" t="str">
         <x:v>MAE</x:v>
       </x:c>
-      <x:c r="W2" s="5" t="str">
-        <x:v>MSE</x:v>
-      </x:c>
-      <x:c r="X2" s="5" t="str">
-        <x:v>MAE</x:v>
-      </x:c>
     </x:row>
     <x:row r="3" ht="20" customHeight="1">
       <x:c r="A3" s="5" t="str">
@@ -468,67 +460,53 @@
       <x:c r="C3" s="8" t="n">
         <x:v>0.359</x:v>
       </x:c>
-      <x:c r="D3" s="9" t="n">
+      <x:c r="D3" s="8" t="n">
         <x:v>0.389</x:v>
       </x:c>
       <x:c r="E3" s="6" t="n">
+        <x:v>0.369</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="n">
+        <x:v>0.393</x:v>
+      </x:c>
+      <x:c r="G3" s="10" t="n">
+        <x:v>0.366</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="n">
+        <x:v>0.392</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="n">
         <x:v>0.374</x:v>
       </x:c>
-      <x:c r="F3" s="9" t="n">
-        <x:v>0.389</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="n">
-        <x:v>0.369</x:v>
-      </x:c>
-      <x:c r="H3" s="6" t="n">
-        <x:v>0.393</x:v>
-      </x:c>
-      <x:c r="I3" s="9" t="n">
-        <x:v>0.366</x:v>
-      </x:c>
-      <x:c r="J3" s="6" t="n">
-        <x:v>0.392</x:v>
-      </x:c>
-      <x:c r="K3" s="6" t="n">
-        <x:v>0.374</x:v>
-      </x:c>
-      <x:c r="L3" s="6" t="n">
+      <x:c r="J3" s="10" t="n">
         <x:v>0.391</x:v>
       </x:c>
+      <x:c r="K3" s="6"/>
+      <x:c r="L3" s="6"/>
       <x:c r="M3" s="6" t="n">
+        <x:v>0.386</x:v>
+      </x:c>
+      <x:c r="N3" s="6" t="n">
+        <x:v>0.404</x:v>
+      </x:c>
+      <x:c r="O3" s="6" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="P3" s="6" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="Q3" s="6" t="n">
+        <x:v>0.414</x:v>
+      </x:c>
+      <x:c r="R3" s="6" t="n">
+        <x:v>0.419</x:v>
+      </x:c>
+      <x:c r="S3" s="6"/>
+      <x:c r="T3" s="6"/>
+      <x:c r="U3" s="6" t="n">
         <x:v>0.376</x:v>
       </x:c>
-      <x:c r="N3" s="8" t="n">
-        <x:v>0.386</x:v>
-      </x:c>
-      <x:c r="O3" s="6" t="n">
-        <x:v>0.386</x:v>
-      </x:c>
-      <x:c r="P3" s="6" t="n">
-        <x:v>0.404</x:v>
-      </x:c>
-      <x:c r="Q3" s="6" t="n">
-        <x:v>0.38</x:v>
-      </x:c>
-      <x:c r="R3" s="6" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="S3" s="6" t="n">
-        <x:v>0.414</x:v>
-      </x:c>
-      <x:c r="T3" s="6" t="n">
-        <x:v>0.419</x:v>
-      </x:c>
-      <x:c r="U3" s="6" t="n">
-        <x:v>0.386</x:v>
-      </x:c>
       <x:c r="V3" s="6" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="W3" s="6" t="n">
-        <x:v>0.376</x:v>
-      </x:c>
-      <x:c r="X3" s="6" t="n">
         <x:v>0.419</x:v>
       </x:c>
     </x:row>
@@ -542,67 +520,53 @@
       <x:c r="C4" s="8" t="n">
         <x:v>0.411</x:v>
       </x:c>
-      <x:c r="D4" s="9" t="n">
+      <x:c r="D4" s="8" t="n">
         <x:v>0.416</x:v>
       </x:c>
       <x:c r="E4" s="6" t="n">
-        <x:v>0.427</x:v>
+        <x:v>0.423</x:v>
       </x:c>
       <x:c r="F4" s="6" t="n">
-        <x:v>0.418</x:v>
+        <x:v>0.426</x:v>
       </x:c>
       <x:c r="G4" s="6" t="n">
-        <x:v>0.423</x:v>
-      </x:c>
-      <x:c r="H4" s="6" t="n">
-        <x:v>0.426</x:v>
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="H4" s="10" t="n">
+        <x:v>0.421</x:v>
       </x:c>
       <x:c r="I4" s="6" t="n">
-        <x:v>0.422</x:v>
-      </x:c>
-      <x:c r="J4" s="6" t="n">
+        <x:v>0.424</x:v>
+      </x:c>
+      <x:c r="J4" s="10" t="n">
         <x:v>0.421</x:v>
       </x:c>
-      <x:c r="K4" s="6" t="n">
-        <x:v>0.424</x:v>
-      </x:c>
-      <x:c r="L4" s="6" t="n">
-        <x:v>0.421</x:v>
-      </x:c>
-      <x:c r="M4" s="9" t="n">
-        <x:v>0.417</x:v>
-      </x:c>
-      <x:c r="N4" s="8" t="n">
-        <x:v>0.407</x:v>
+      <x:c r="K4" s="6"/>
+      <x:c r="L4" s="6"/>
+      <x:c r="M4" s="6" t="n">
+        <x:v>0.441</x:v>
+      </x:c>
+      <x:c r="N4" s="6" t="n">
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="O4" s="6" t="n">
-        <x:v>0.441</x:v>
+        <x:v>0.438</x:v>
       </x:c>
       <x:c r="P4" s="6" t="n">
-        <x:v>0.43</x:v>
+        <x:v>0.428</x:v>
       </x:c>
       <x:c r="Q4" s="6" t="n">
-        <x:v>0.438</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="R4" s="6" t="n">
-        <x:v>0.428</x:v>
-      </x:c>
-      <x:c r="S4" s="6" t="n">
-        <x:v>0.46</x:v>
-      </x:c>
-      <x:c r="T4" s="6" t="n">
         <x:v>0.445</x:v>
       </x:c>
-      <x:c r="U4" s="6" t="n">
-        <x:v>0.437</x:v>
+      <x:c r="S4" s="6"/>
+      <x:c r="T4" s="6"/>
+      <x:c r="U4" s="10" t="n">
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="V4" s="6" t="n">
-        <x:v>0.432</x:v>
-      </x:c>
-      <x:c r="W4" s="6" t="n">
-        <x:v>0.42</x:v>
-      </x:c>
-      <x:c r="X4" s="6" t="n">
         <x:v>0.448</x:v>
       </x:c>
     </x:row>
@@ -616,67 +580,53 @@
       <x:c r="C5" s="8" t="n">
         <x:v>0.426</x:v>
       </x:c>
-      <x:c r="D5" s="9" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>0.43</x:v>
       </x:c>
       <x:c r="E5" s="6" t="n">
-        <x:v>0.468</x:v>
+        <x:v>0.466</x:v>
       </x:c>
       <x:c r="F5" s="6" t="n">
+        <x:v>0.448</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="n">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="n">
         <x:v>0.438</x:v>
       </x:c>
-      <x:c r="G5" s="6" t="n">
-        <x:v>0.466</x:v>
-      </x:c>
-      <x:c r="H5" s="6" t="n">
-        <x:v>0.448</x:v>
-      </x:c>
-      <x:c r="I5" s="9" t="n">
-        <x:v>0.44</x:v>
+      <x:c r="I5" s="6" t="n">
+        <x:v>0.464</x:v>
       </x:c>
       <x:c r="J5" s="6" t="n">
-        <x:v>0.438</x:v>
-      </x:c>
-      <x:c r="K5" s="6" t="n">
-        <x:v>0.464</x:v>
-      </x:c>
-      <x:c r="L5" s="6" t="n">
         <x:v>0.441</x:v>
       </x:c>
+      <x:c r="K5" s="6"/>
+      <x:c r="L5" s="6"/>
       <x:c r="M5" s="6" t="n">
-        <x:v>0.449</x:v>
-      </x:c>
-      <x:c r="N5" s="8" t="n">
-        <x:v>0.425</x:v>
+        <x:v>0.487</x:v>
+      </x:c>
+      <x:c r="N5" s="6" t="n">
+        <x:v>0.458</x:v>
       </x:c>
       <x:c r="O5" s="6" t="n">
-        <x:v>0.487</x:v>
+        <x:v>0.478</x:v>
       </x:c>
       <x:c r="P5" s="6" t="n">
-        <x:v>0.458</x:v>
+        <x:v>0.451</x:v>
       </x:c>
       <x:c r="Q5" s="6" t="n">
-        <x:v>0.478</x:v>
+        <x:v>0.469</x:v>
       </x:c>
       <x:c r="R5" s="6" t="n">
-        <x:v>0.451</x:v>
-      </x:c>
-      <x:c r="S5" s="6" t="n">
-        <x:v>0.469</x:v>
-      </x:c>
-      <x:c r="T5" s="6" t="n">
         <x:v>0.457</x:v>
       </x:c>
+      <x:c r="S5" s="6"/>
+      <x:c r="T5" s="6"/>
       <x:c r="U5" s="6" t="n">
-        <x:v>0.481</x:v>
+        <x:v>0.459</x:v>
       </x:c>
       <x:c r="V5" s="6" t="n">
-        <x:v>0.459</x:v>
-      </x:c>
-      <x:c r="W5" s="6" t="n">
-        <x:v>0.459</x:v>
-      </x:c>
-      <x:c r="X5" s="6" t="n">
         <x:v>0.465</x:v>
       </x:c>
     </x:row>
@@ -690,67 +640,53 @@
       <x:c r="C6" s="8" t="n">
         <x:v>0.453</x:v>
       </x:c>
-      <x:c r="D6" s="9" t="n">
+      <x:c r="D6" s="8" t="n">
         <x:v>0.454</x:v>
       </x:c>
-      <x:c r="E6" s="9" t="n">
-        <x:v>0.455</x:v>
-      </x:c>
-      <x:c r="F6" s="8" t="n">
-        <x:v>0.45</x:v>
-      </x:c>
-      <x:c r="G6" s="6" t="n">
+      <x:c r="E6" s="6" t="n">
         <x:v>0.499</x:v>
       </x:c>
-      <x:c r="H6" s="6" t="n">
+      <x:c r="F6" s="6" t="n">
         <x:v>0.482</x:v>
       </x:c>
+      <x:c r="G6" s="10" t="n">
+        <x:v>0.463</x:v>
+      </x:c>
+      <x:c r="H6" s="10" t="n">
+        <x:v>0.462</x:v>
+      </x:c>
       <x:c r="I6" s="6" t="n">
-        <x:v>0.463</x:v>
+        <x:v>0.47</x:v>
       </x:c>
       <x:c r="J6" s="6" t="n">
-        <x:v>0.462</x:v>
-      </x:c>
-      <x:c r="K6" s="6" t="n">
-        <x:v>0.47</x:v>
-      </x:c>
-      <x:c r="L6" s="6" t="n">
         <x:v>0.466</x:v>
       </x:c>
+      <x:c r="K6" s="6"/>
+      <x:c r="L6" s="6"/>
       <x:c r="M6" s="6" t="n">
-        <x:v>0.47</x:v>
+        <x:v>0.503</x:v>
       </x:c>
       <x:c r="N6" s="6" t="n">
-        <x:v>0.456</x:v>
+        <x:v>0.491</x:v>
       </x:c>
       <x:c r="O6" s="6" t="n">
-        <x:v>0.503</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="P6" s="6" t="n">
-        <x:v>0.491</x:v>
+        <x:v>0.496</x:v>
       </x:c>
       <x:c r="Q6" s="6" t="n">
-        <x:v>0.54</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="R6" s="6" t="n">
-        <x:v>0.496</x:v>
-      </x:c>
-      <x:c r="S6" s="6" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="T6" s="6" t="n">
         <x:v>0.488</x:v>
       </x:c>
+      <x:c r="S6" s="6"/>
+      <x:c r="T6" s="6"/>
       <x:c r="U6" s="6" t="n">
-        <x:v>0.519</x:v>
+        <x:v>0.506</x:v>
       </x:c>
       <x:c r="V6" s="6" t="n">
-        <x:v>0.516</x:v>
-      </x:c>
-      <x:c r="W6" s="6" t="n">
-        <x:v>0.506</x:v>
-      </x:c>
-      <x:c r="X6" s="6" t="n">
         <x:v>0.507</x:v>
       </x:c>
     </x:row>
@@ -764,67 +700,61 @@
       <x:c r="C7" s="8" t="n">
         <x:v>0.412</x:v>
       </x:c>
-      <x:c r="D7" s="9" t="n">
+      <x:c r="D7" s="8" t="n">
         <x:v>0.422</x:v>
       </x:c>
       <x:c r="E7" s="6" t="n">
-        <x:v>0.431</x:v>
+        <x:v>0.439</x:v>
       </x:c>
       <x:c r="F7" s="6" t="n">
-        <x:v>0.423</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="n">
-        <x:v>0.439</x:v>
-      </x:c>
-      <x:c r="H7" s="6" t="n">
         <x:v>0.437</x:v>
       </x:c>
-      <x:c r="I7" s="9" t="n">
+      <x:c r="G7" s="10" t="n">
         <x:v>0.422</x:v>
       </x:c>
+      <x:c r="H7" s="10" t="n">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="n">
+        <x:v>0.433</x:v>
+      </x:c>
       <x:c r="J7" s="6" t="n">
+        <x:v>0.429</x:v>
+      </x:c>
+      <x:c r="K7" s="6" t="n">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="n">
         <x:v>0.428</x:v>
       </x:c>
-      <x:c r="K7" s="6" t="n">
-        <x:v>0.433</x:v>
-      </x:c>
-      <x:c r="L7" s="6" t="n">
-        <x:v>0.429</x:v>
-      </x:c>
       <x:c r="M7" s="6" t="n">
-        <x:v>0.428</x:v>
-      </x:c>
-      <x:c r="N7" s="8" t="n">
-        <x:v>0.418</x:v>
+        <x:v>0.454</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="n">
+        <x:v>0.445</x:v>
       </x:c>
       <x:c r="O7" s="6" t="n">
-        <x:v>0.454</x:v>
+        <x:v>0.459</x:v>
       </x:c>
       <x:c r="P7" s="6" t="n">
-        <x:v>0.445</x:v>
+        <x:v>0.443</x:v>
       </x:c>
       <x:c r="Q7" s="6" t="n">
-        <x:v>0.459</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="R7" s="6" t="n">
-        <x:v>0.443</x:v>
+        <x:v>0.452</x:v>
       </x:c>
       <x:c r="S7" s="6" t="n">
-        <x:v>0.46</x:v>
+        <x:v>0.458</x:v>
       </x:c>
       <x:c r="T7" s="6" t="n">
-        <x:v>0.452</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="U7" s="6" t="n">
-        <x:v>0.455</x:v>
+        <x:v>0.44</x:v>
       </x:c>
       <x:c r="V7" s="6" t="n">
-        <x:v>0.451</x:v>
-      </x:c>
-      <x:c r="W7" s="6" t="n">
-        <x:v>0.44</x:v>
-      </x:c>
-      <x:c r="X7" s="6" t="n">
         <x:v>0.459</x:v>
       </x:c>
     </x:row>
@@ -838,67 +768,53 @@
       <x:c r="C8" s="8" t="n">
         <x:v>0.301</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="n">
+      <x:c r="D8" s="8" t="n">
         <x:v>0.346</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="n">
-        <x:v>0.303</x:v>
-      </x:c>
-      <x:c r="F8" s="8" t="n">
-        <x:v>0.336</x:v>
+      <x:c r="E8" s="10" t="n">
+        <x:v>0.318</x:v>
+      </x:c>
+      <x:c r="F8" s="10" t="n">
+        <x:v>0.357</x:v>
       </x:c>
       <x:c r="G8" s="6" t="n">
-        <x:v>0.318</x:v>
+        <x:v>0.321</x:v>
       </x:c>
       <x:c r="H8" s="6" t="n">
-        <x:v>0.357</x:v>
+        <x:v>0.361</x:v>
       </x:c>
       <x:c r="I8" s="6" t="n">
         <x:v>0.321</x:v>
       </x:c>
       <x:c r="J8" s="6" t="n">
-        <x:v>0.361</x:v>
-      </x:c>
-      <x:c r="K8" s="6" t="n">
-        <x:v>0.321</x:v>
-      </x:c>
-      <x:c r="L8" s="6" t="n">
         <x:v>0.36</x:v>
       </x:c>
+      <x:c r="K8" s="6"/>
+      <x:c r="L8" s="6"/>
       <x:c r="M8" s="6" t="n">
-        <x:v>0.311</x:v>
-      </x:c>
-      <x:c r="N8" s="9" t="n">
-        <x:v>0.346</x:v>
+        <x:v>0.334</x:v>
+      </x:c>
+      <x:c r="N8" s="6" t="n">
+        <x:v>0.368</x:v>
       </x:c>
       <x:c r="O8" s="6" t="n">
-        <x:v>0.334</x:v>
+        <x:v>0.322</x:v>
       </x:c>
       <x:c r="P8" s="6" t="n">
-        <x:v>0.368</x:v>
+        <x:v>0.362</x:v>
       </x:c>
       <x:c r="Q8" s="6" t="n">
-        <x:v>0.322</x:v>
+        <x:v>0.329</x:v>
       </x:c>
       <x:c r="R8" s="6" t="n">
-        <x:v>0.362</x:v>
-      </x:c>
-      <x:c r="S8" s="6" t="n">
-        <x:v>0.329</x:v>
-      </x:c>
-      <x:c r="T8" s="6" t="n">
         <x:v>0.367</x:v>
       </x:c>
+      <x:c r="S8" s="6"/>
+      <x:c r="T8" s="6"/>
       <x:c r="U8" s="6" t="n">
-        <x:v>0.345</x:v>
+        <x:v>0.379</x:v>
       </x:c>
       <x:c r="V8" s="6" t="n">
-        <x:v>0.372</x:v>
-      </x:c>
-      <x:c r="W8" s="6" t="n">
-        <x:v>0.379</x:v>
-      </x:c>
-      <x:c r="X8" s="6" t="n">
         <x:v>0.419</x:v>
       </x:c>
     </x:row>
@@ -912,67 +828,53 @@
       <x:c r="C9" s="8" t="n">
         <x:v>0.347</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="n">
+      <x:c r="D9" s="8" t="n">
         <x:v>0.374</x:v>
       </x:c>
       <x:c r="E9" s="6" t="n">
-        <x:v>0.359</x:v>
-      </x:c>
-      <x:c r="F9" s="8" t="n">
-        <x:v>0.364</x:v>
-      </x:c>
-      <x:c r="G9" s="6" t="n">
         <x:v>0.362</x:v>
       </x:c>
+      <x:c r="F9" s="10" t="n">
+        <x:v>0.379</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="n">
+        <x:v>0.36</x:v>
+      </x:c>
       <x:c r="H9" s="6" t="n">
-        <x:v>0.379</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="I9" s="6" t="n">
-        <x:v>0.36</x:v>
+        <x:v>0.363</x:v>
       </x:c>
       <x:c r="J9" s="6" t="n">
-        <x:v>0.38</x:v>
-      </x:c>
-      <x:c r="K9" s="6" t="n">
-        <x:v>0.363</x:v>
-      </x:c>
-      <x:c r="L9" s="6" t="n">
         <x:v>0.382</x:v>
       </x:c>
-      <x:c r="M9" s="9" t="n">
-        <x:v>0.348</x:v>
-      </x:c>
-      <x:c r="N9" s="9" t="n">
-        <x:v>0.368</x:v>
+      <x:c r="K9" s="6"/>
+      <x:c r="L9" s="6"/>
+      <x:c r="M9" s="6" t="n">
+        <x:v>0.377</x:v>
+      </x:c>
+      <x:c r="N9" s="6" t="n">
+        <x:v>0.391</x:v>
       </x:c>
       <x:c r="O9" s="6" t="n">
-        <x:v>0.377</x:v>
+        <x:v>0.369</x:v>
       </x:c>
       <x:c r="P9" s="6" t="n">
-        <x:v>0.391</x:v>
+        <x:v>0.386</x:v>
       </x:c>
       <x:c r="Q9" s="6" t="n">
-        <x:v>0.369</x:v>
+        <x:v>0.367</x:v>
       </x:c>
       <x:c r="R9" s="6" t="n">
-        <x:v>0.386</x:v>
-      </x:c>
-      <x:c r="S9" s="6" t="n">
-        <x:v>0.367</x:v>
-      </x:c>
-      <x:c r="T9" s="6" t="n">
         <x:v>0.385</x:v>
       </x:c>
+      <x:c r="S9" s="6"/>
+      <x:c r="T9" s="6"/>
       <x:c r="U9" s="6" t="n">
-        <x:v>0.38</x:v>
+        <x:v>0.426</x:v>
       </x:c>
       <x:c r="V9" s="6" t="n">
-        <x:v>0.389</x:v>
-      </x:c>
-      <x:c r="W9" s="6" t="n">
-        <x:v>0.426</x:v>
-      </x:c>
-      <x:c r="X9" s="6" t="n">
         <x:v>0.441</x:v>
       </x:c>
     </x:row>
@@ -986,67 +888,53 @@
       <x:c r="C10" s="8" t="n">
         <x:v>0.376</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="n">
+      <x:c r="D10" s="8" t="n">
         <x:v>0.397</x:v>
       </x:c>
       <x:c r="E10" s="6" t="n">
-        <x:v>0.393</x:v>
-      </x:c>
-      <x:c r="F10" s="8" t="n">
-        <x:v>0.387</x:v>
-      </x:c>
-      <x:c r="G10" s="6" t="n">
         <x:v>0.396</x:v>
       </x:c>
+      <x:c r="F10" s="6" t="n">
+        <x:v>0.405</x:v>
+      </x:c>
+      <x:c r="G10" s="10" t="n">
+        <x:v>0.39</x:v>
+      </x:c>
       <x:c r="H10" s="6" t="n">
-        <x:v>0.405</x:v>
+        <x:v>0.404</x:v>
       </x:c>
       <x:c r="I10" s="6" t="n">
-        <x:v>0.39</x:v>
-      </x:c>
-      <x:c r="J10" s="6" t="n">
-        <x:v>0.404</x:v>
-      </x:c>
-      <x:c r="K10" s="6" t="n">
         <x:v>0.395</x:v>
       </x:c>
-      <x:c r="L10" s="6" t="n">
+      <x:c r="J10" s="10" t="n">
         <x:v>0.403</x:v>
       </x:c>
-      <x:c r="M10" s="9" t="n">
-        <x:v>0.388</x:v>
-      </x:c>
-      <x:c r="N10" s="9" t="n">
-        <x:v>0.391</x:v>
+      <x:c r="K10" s="6"/>
+      <x:c r="L10" s="6"/>
+      <x:c r="M10" s="6" t="n">
+        <x:v>0.426</x:v>
+      </x:c>
+      <x:c r="N10" s="6" t="n">
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="O10" s="6" t="n">
-        <x:v>0.426</x:v>
+        <x:v>0.392</x:v>
       </x:c>
       <x:c r="P10" s="6" t="n">
-        <x:v>0.42</x:v>
+        <x:v>0.407</x:v>
       </x:c>
       <x:c r="Q10" s="6" t="n">
-        <x:v>0.392</x:v>
+        <x:v>0.399</x:v>
       </x:c>
       <x:c r="R10" s="6" t="n">
-        <x:v>0.407</x:v>
-      </x:c>
-      <x:c r="S10" s="6" t="n">
-        <x:v>0.399</x:v>
-      </x:c>
-      <x:c r="T10" s="6" t="n">
         <x:v>0.41</x:v>
       </x:c>
+      <x:c r="S10" s="6"/>
+      <x:c r="T10" s="6"/>
       <x:c r="U10" s="6" t="n">
-        <x:v>0.413</x:v>
+        <x:v>0.445</x:v>
       </x:c>
       <x:c r="V10" s="6" t="n">
-        <x:v>0.413</x:v>
-      </x:c>
-      <x:c r="W10" s="6" t="n">
-        <x:v>0.445</x:v>
-      </x:c>
-      <x:c r="X10" s="6" t="n">
         <x:v>0.459</x:v>
       </x:c>
     </x:row>
@@ -1060,67 +948,53 @@
       <x:c r="C11" s="8" t="n">
         <x:v>0.436</x:v>
       </x:c>
-      <x:c r="D11" s="9" t="n">
+      <x:c r="D11" s="8" t="n">
         <x:v>0.431</x:v>
       </x:c>
       <x:c r="E11" s="6" t="n">
-        <x:v>0.467</x:v>
-      </x:c>
-      <x:c r="F11" s="9" t="n">
-        <x:v>0.431</x:v>
-      </x:c>
-      <x:c r="G11" s="6" t="n">
         <x:v>0.457</x:v>
       </x:c>
-      <x:c r="H11" s="6" t="n">
+      <x:c r="F11" s="6" t="n">
         <x:v>0.444</x:v>
       </x:c>
-      <x:c r="I11" s="9" t="n">
+      <x:c r="G11" s="10" t="n">
         <x:v>0.454</x:v>
       </x:c>
-      <x:c r="J11" s="6" t="n">
+      <x:c r="H11" s="10" t="n">
         <x:v>0.438</x:v>
       </x:c>
-      <x:c r="K11" s="6" t="n">
+      <x:c r="I11" s="6" t="n">
         <x:v>0.462</x:v>
       </x:c>
-      <x:c r="L11" s="6" t="n">
+      <x:c r="J11" s="10" t="n">
         <x:v>0.438</x:v>
       </x:c>
+      <x:c r="K11" s="6"/>
+      <x:c r="L11" s="6"/>
       <x:c r="M11" s="6" t="n">
-        <x:v>0.461</x:v>
-      </x:c>
-      <x:c r="N11" s="8" t="n">
-        <x:v>0.43</x:v>
+        <x:v>0.491</x:v>
+      </x:c>
+      <x:c r="N11" s="6" t="n">
+        <x:v>0.459</x:v>
       </x:c>
       <x:c r="O11" s="6" t="n">
-        <x:v>0.491</x:v>
+        <x:v>0.456</x:v>
       </x:c>
       <x:c r="P11" s="6" t="n">
-        <x:v>0.459</x:v>
-      </x:c>
-      <x:c r="Q11" s="6" t="n">
-        <x:v>0.456</x:v>
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="Q11" s="10" t="n">
+        <x:v>0.454</x:v>
       </x:c>
       <x:c r="R11" s="6" t="n">
-        <x:v>0.445</x:v>
-      </x:c>
-      <x:c r="S11" s="9" t="n">
-        <x:v>0.454</x:v>
-      </x:c>
-      <x:c r="T11" s="6" t="n">
         <x:v>0.439</x:v>
       </x:c>
+      <x:c r="S11" s="6"/>
+      <x:c r="T11" s="6"/>
       <x:c r="U11" s="6" t="n">
-        <x:v>0.474</x:v>
+        <x:v>0.543</x:v>
       </x:c>
       <x:c r="V11" s="6" t="n">
-        <x:v>0.453</x:v>
-      </x:c>
-      <x:c r="W11" s="6" t="n">
-        <x:v>0.543</x:v>
-      </x:c>
-      <x:c r="X11" s="6" t="n">
         <x:v>0.49</x:v>
       </x:c>
     </x:row>
@@ -1134,67 +1008,61 @@
       <x:c r="C12" s="8" t="n">
         <x:v>0.365</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="n">
+      <x:c r="D12" s="8" t="n">
         <x:v>0.387</x:v>
       </x:c>
       <x:c r="E12" s="6" t="n">
-        <x:v>0.38</x:v>
-      </x:c>
-      <x:c r="F12" s="8" t="n">
-        <x:v>0.379</x:v>
-      </x:c>
-      <x:c r="G12" s="6" t="n">
         <x:v>0.383</x:v>
       </x:c>
-      <x:c r="H12" s="6" t="n">
+      <x:c r="F12" s="6" t="n">
         <x:v>0.396</x:v>
       </x:c>
+      <x:c r="G12" s="10" t="n">
+        <x:v>0.381</x:v>
+      </x:c>
+      <x:c r="H12" s="10" t="n">
+        <x:v>0.395</x:v>
+      </x:c>
       <x:c r="I12" s="6" t="n">
-        <x:v>0.381</x:v>
-      </x:c>
-      <x:c r="J12" s="6" t="n">
+        <x:v>0.385</x:v>
+      </x:c>
+      <x:c r="J12" s="10" t="n">
         <x:v>0.395</x:v>
       </x:c>
       <x:c r="K12" s="6" t="n">
-        <x:v>0.385</x:v>
+        <x:v>0.392</x:v>
       </x:c>
       <x:c r="L12" s="6" t="n">
-        <x:v>0.395</x:v>
-      </x:c>
-      <x:c r="M12" s="9" t="n">
-        <x:v>0.377</x:v>
-      </x:c>
-      <x:c r="N12" s="9" t="n">
-        <x:v>0.383</x:v>
+        <x:v>0.397</x:v>
+      </x:c>
+      <x:c r="M12" s="6" t="n">
+        <x:v>0.407</x:v>
+      </x:c>
+      <x:c r="N12" s="6" t="n">
+        <x:v>0.409</x:v>
       </x:c>
       <x:c r="O12" s="6" t="n">
-        <x:v>0.407</x:v>
+        <x:v>0.384</x:v>
       </x:c>
       <x:c r="P12" s="6" t="n">
-        <x:v>0.409</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="Q12" s="6" t="n">
-        <x:v>0.384</x:v>
+        <x:v>0.387</x:v>
       </x:c>
       <x:c r="R12" s="6" t="n">
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="S12" s="6" t="n">
-        <x:v>0.387</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="T12" s="6" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.406</x:v>
       </x:c>
       <x:c r="U12" s="6" t="n">
-        <x:v>0.403</x:v>
+        <x:v>0.448</x:v>
       </x:c>
       <x:c r="V12" s="6" t="n">
-        <x:v>0.406</x:v>
-      </x:c>
-      <x:c r="W12" s="6" t="n">
-        <x:v>0.448</x:v>
-      </x:c>
-      <x:c r="X12" s="6" t="n">
         <x:v>0.452</x:v>
       </x:c>
     </x:row>
@@ -1205,70 +1073,56 @@
       <x:c r="B13" s="4" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C13" s="9" t="n">
+      <x:c r="C13" s="8" t="n">
         <x:v>0.272</x:v>
       </x:c>
-      <x:c r="D13" s="9" t="n">
+      <x:c r="D13" s="8" t="n">
         <x:v>0.334</x:v>
       </x:c>
       <x:c r="E13" s="6" t="n">
-        <x:v>0.289</x:v>
-      </x:c>
-      <x:c r="F13" s="9" t="n">
-        <x:v>0.334</x:v>
-      </x:c>
-      <x:c r="G13" s="6" t="n">
         <x:v>0.301</x:v>
       </x:c>
-      <x:c r="H13" s="6" t="n">
+      <x:c r="F13" s="6" t="n">
         <x:v>0.349</x:v>
       </x:c>
+      <x:c r="G13" s="10" t="n">
+        <x:v>0.281</x:v>
+      </x:c>
+      <x:c r="H13" s="10" t="n">
+        <x:v>0.338</x:v>
+      </x:c>
       <x:c r="I13" s="6" t="n">
-        <x:v>0.281</x:v>
-      </x:c>
-      <x:c r="J13" s="6" t="n">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="J13" s="10" t="n">
         <x:v>0.338</x:v>
       </x:c>
-      <x:c r="K13" s="6" t="n">
-        <x:v>0.29</x:v>
-      </x:c>
-      <x:c r="L13" s="6" t="n">
-        <x:v>0.338</x:v>
-      </x:c>
-      <x:c r="M13" s="8" t="n">
-        <x:v>0.233</x:v>
-      </x:c>
-      <x:c r="N13" s="8" t="n">
-        <x:v>0.3</x:v>
+      <x:c r="K13" s="6"/>
+      <x:c r="L13" s="6"/>
+      <x:c r="M13" s="6" t="n">
+        <x:v>0.297</x:v>
+      </x:c>
+      <x:c r="N13" s="6" t="n">
+        <x:v>0.349</x:v>
       </x:c>
       <x:c r="O13" s="6" t="n">
-        <x:v>0.297</x:v>
+        <x:v>0.293</x:v>
       </x:c>
       <x:c r="P13" s="6" t="n">
-        <x:v>0.349</x:v>
+        <x:v>0.344</x:v>
       </x:c>
       <x:c r="Q13" s="6" t="n">
-        <x:v>0.293</x:v>
+        <x:v>0.302</x:v>
       </x:c>
       <x:c r="R13" s="6" t="n">
-        <x:v>0.344</x:v>
-      </x:c>
-      <x:c r="S13" s="6" t="n">
-        <x:v>0.302</x:v>
-      </x:c>
-      <x:c r="T13" s="6" t="n">
         <x:v>0.348</x:v>
       </x:c>
+      <x:c r="S13" s="6"/>
+      <x:c r="T13" s="6"/>
       <x:c r="U13" s="6" t="n">
-        <x:v>0.333</x:v>
+        <x:v>0.358</x:v>
       </x:c>
       <x:c r="V13" s="6" t="n">
-        <x:v>0.387</x:v>
-      </x:c>
-      <x:c r="W13" s="6" t="n">
-        <x:v>0.358</x:v>
-      </x:c>
-      <x:c r="X13" s="6" t="n">
         <x:v>0.397</x:v>
       </x:c>
     </x:row>
@@ -1279,70 +1133,56 @@
       <x:c r="B14" s="4" t="n">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="C14" s="9" t="n">
+      <x:c r="C14" s="8" t="n">
         <x:v>0.353</x:v>
       </x:c>
-      <x:c r="D14" s="9" t="n">
+      <x:c r="D14" s="8" t="n">
         <x:v>0.385</x:v>
       </x:c>
       <x:c r="E14" s="6" t="n">
-        <x:v>0.366</x:v>
-      </x:c>
-      <x:c r="F14" s="9" t="n">
-        <x:v>0.385</x:v>
-      </x:c>
-      <x:c r="G14" s="6" t="n">
         <x:v>0.369</x:v>
       </x:c>
-      <x:c r="H14" s="6" t="n">
+      <x:c r="F14" s="6" t="n">
         <x:v>0.392</x:v>
       </x:c>
+      <x:c r="G14" s="10" t="n">
+        <x:v>0.355</x:v>
+      </x:c>
+      <x:c r="H14" s="10" t="n">
+        <x:v>0.387</x:v>
+      </x:c>
       <x:c r="I14" s="6" t="n">
-        <x:v>0.355</x:v>
+        <x:v>0.374</x:v>
       </x:c>
       <x:c r="J14" s="6" t="n">
-        <x:v>0.387</x:v>
-      </x:c>
-      <x:c r="K14" s="6" t="n">
-        <x:v>0.374</x:v>
-      </x:c>
-      <x:c r="L14" s="6" t="n">
         <x:v>0.39</x:v>
       </x:c>
-      <x:c r="M14" s="8" t="n">
-        <x:v>0.291</x:v>
-      </x:c>
-      <x:c r="N14" s="8" t="n">
-        <x:v>0.338</x:v>
+      <x:c r="K14" s="6"/>
+      <x:c r="L14" s="6"/>
+      <x:c r="M14" s="6" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="N14" s="6" t="n">
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="O14" s="6" t="n">
-        <x:v>0.38</x:v>
+        <x:v>0.378</x:v>
       </x:c>
       <x:c r="P14" s="6" t="n">
+        <x:v>0.395</x:v>
+      </x:c>
+      <x:c r="Q14" s="6" t="n">
+        <x:v>0.388</x:v>
+      </x:c>
+      <x:c r="R14" s="6" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="Q14" s="6" t="n">
-        <x:v>0.378</x:v>
-      </x:c>
-      <x:c r="R14" s="6" t="n">
-        <x:v>0.395</x:v>
-      </x:c>
-      <x:c r="S14" s="6" t="n">
-        <x:v>0.388</x:v>
-      </x:c>
-      <x:c r="T14" s="6" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
+      <x:c r="S14" s="6"/>
+      <x:c r="T14" s="6"/>
       <x:c r="U14" s="6" t="n">
-        <x:v>0.477</x:v>
+        <x:v>0.429</x:v>
       </x:c>
       <x:c r="V14" s="6" t="n">
-        <x:v>0.476</x:v>
-      </x:c>
-      <x:c r="W14" s="6" t="n">
-        <x:v>0.429</x:v>
-      </x:c>
-      <x:c r="X14" s="6" t="n">
         <x:v>0.439</x:v>
       </x:c>
     </x:row>
@@ -1353,70 +1193,56 @@
       <x:c r="B15" s="4" t="n">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="C15" s="9" t="n">
+      <x:c r="C15" s="8" t="n">
         <x:v>0.361</x:v>
       </x:c>
-      <x:c r="D15" s="9" t="n">
+      <x:c r="D15" s="8" t="n">
         <x:v>0.397</x:v>
       </x:c>
       <x:c r="E15" s="6" t="n">
-        <x:v>0.413</x:v>
+        <x:v>0.423</x:v>
       </x:c>
       <x:c r="F15" s="6" t="n">
-        <x:v>0.421</x:v>
-      </x:c>
-      <x:c r="G15" s="6" t="n">
-        <x:v>0.423</x:v>
-      </x:c>
-      <x:c r="H15" s="6" t="n">
         <x:v>0.43</x:v>
       </x:c>
+      <x:c r="G15" s="10" t="n">
+        <x:v>0.365</x:v>
+      </x:c>
+      <x:c r="H15" s="10" t="n">
+        <x:v>0.401</x:v>
+      </x:c>
       <x:c r="I15" s="6" t="n">
-        <x:v>0.365</x:v>
+        <x:v>0.406</x:v>
       </x:c>
       <x:c r="J15" s="6" t="n">
-        <x:v>0.401</x:v>
-      </x:c>
-      <x:c r="K15" s="6" t="n">
-        <x:v>0.406</x:v>
-      </x:c>
-      <x:c r="L15" s="6" t="n">
         <x:v>0.42</x:v>
       </x:c>
-      <x:c r="M15" s="8" t="n">
-        <x:v>0.344</x:v>
-      </x:c>
-      <x:c r="N15" s="8" t="n">
-        <x:v>0.377</x:v>
+      <x:c r="K15" s="6"/>
+      <x:c r="L15" s="6"/>
+      <x:c r="M15" s="6" t="n">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="N15" s="6" t="n">
+        <x:v>0.432</x:v>
       </x:c>
       <x:c r="O15" s="6" t="n">
-        <x:v>0.428</x:v>
+        <x:v>0.429</x:v>
       </x:c>
       <x:c r="P15" s="6" t="n">
-        <x:v>0.432</x:v>
+        <x:v>0.437</x:v>
       </x:c>
       <x:c r="Q15" s="6" t="n">
-        <x:v>0.429</x:v>
+        <x:v>0.426</x:v>
       </x:c>
       <x:c r="R15" s="6" t="n">
-        <x:v>0.437</x:v>
-      </x:c>
-      <x:c r="S15" s="6" t="n">
-        <x:v>0.426</x:v>
-      </x:c>
-      <x:c r="T15" s="6" t="n">
         <x:v>0.433</x:v>
       </x:c>
+      <x:c r="S15" s="6"/>
+      <x:c r="T15" s="6"/>
       <x:c r="U15" s="6" t="n">
-        <x:v>0.594</x:v>
+        <x:v>0.496</x:v>
       </x:c>
       <x:c r="V15" s="6" t="n">
-        <x:v>0.541</x:v>
-      </x:c>
-      <x:c r="W15" s="6" t="n">
-        <x:v>0.496</x:v>
-      </x:c>
-      <x:c r="X15" s="6" t="n">
         <x:v>0.487</x:v>
       </x:c>
     </x:row>
@@ -1427,70 +1253,56 @@
       <x:c r="B16" s="4" t="n">
         <x:v>720</x:v>
       </x:c>
-      <x:c r="C16" s="9" t="n">
+      <x:c r="C16" s="8" t="n">
         <x:v>0.408</x:v>
       </x:c>
-      <x:c r="D16" s="9" t="n">
+      <x:c r="D16" s="8" t="n">
         <x:v>0.433</x:v>
       </x:c>
       <x:c r="E16" s="6" t="n">
-        <x:v>0.424</x:v>
+        <x:v>0.428</x:v>
       </x:c>
       <x:c r="F16" s="6" t="n">
+        <x:v>0.443</x:v>
+      </x:c>
+      <x:c r="G16" s="10" t="n">
+        <x:v>0.413</x:v>
+      </x:c>
+      <x:c r="H16" s="10" t="n">
+        <x:v>0.436</x:v>
+      </x:c>
+      <x:c r="I16" s="6" t="n">
+        <x:v>0.418</x:v>
+      </x:c>
+      <x:c r="J16" s="6" t="n">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="K16" s="6"/>
+      <x:c r="L16" s="6"/>
+      <x:c r="M16" s="6" t="n">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="N16" s="6" t="n">
+        <x:v>0.445</x:v>
+      </x:c>
+      <x:c r="O16" s="6" t="n">
         <x:v>0.439</x:v>
       </x:c>
-      <x:c r="G16" s="6" t="n">
-        <x:v>0.428</x:v>
-      </x:c>
-      <x:c r="H16" s="6" t="n">
-        <x:v>0.443</x:v>
-      </x:c>
-      <x:c r="I16" s="6" t="n">
-        <x:v>0.413</x:v>
-      </x:c>
-      <x:c r="J16" s="6" t="n">
-        <x:v>0.436</x:v>
-      </x:c>
-      <x:c r="K16" s="6" t="n">
-        <x:v>0.418</x:v>
-      </x:c>
-      <x:c r="L16" s="6" t="n">
-        <x:v>0.437</x:v>
-      </x:c>
-      <x:c r="M16" s="8" t="n">
-        <x:v>0.407</x:v>
-      </x:c>
-      <x:c r="N16" s="8" t="n">
-        <x:v>0.427</x:v>
-      </x:c>
-      <x:c r="O16" s="6" t="n">
-        <x:v>0.427</x:v>
-      </x:c>
       <x:c r="P16" s="6" t="n">
-        <x:v>0.445</x:v>
+        <x:v>0.447</x:v>
       </x:c>
       <x:c r="Q16" s="6" t="n">
-        <x:v>0.439</x:v>
+        <x:v>0.431</x:v>
       </x:c>
       <x:c r="R16" s="6" t="n">
-        <x:v>0.447</x:v>
-      </x:c>
-      <x:c r="S16" s="6" t="n">
-        <x:v>0.431</x:v>
-      </x:c>
-      <x:c r="T16" s="6" t="n">
         <x:v>0.446</x:v>
       </x:c>
+      <x:c r="S16" s="6"/>
+      <x:c r="T16" s="6"/>
       <x:c r="U16" s="6" t="n">
-        <x:v>0.831</x:v>
+        <x:v>0.463</x:v>
       </x:c>
       <x:c r="V16" s="6" t="n">
-        <x:v>0.657</x:v>
-      </x:c>
-      <x:c r="W16" s="6" t="n">
-        <x:v>0.463</x:v>
-      </x:c>
-      <x:c r="X16" s="6" t="n">
         <x:v>0.474</x:v>
       </x:c>
     </x:row>
@@ -1501,70 +1313,64 @@
       <x:c r="B17" s="4" t="str">
         <x:v>AVG</x:v>
       </x:c>
-      <x:c r="C17" s="9" t="n">
+      <x:c r="C17" s="8" t="n">
         <x:v>0.349</x:v>
       </x:c>
-      <x:c r="D17" s="9" t="n">
+      <x:c r="D17" s="8" t="n">
         <x:v>0.387</x:v>
       </x:c>
       <x:c r="E17" s="6" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="n">
+        <x:v>0.403</x:v>
+      </x:c>
+      <x:c r="G17" s="10" t="n">
+        <x:v>0.353</x:v>
+      </x:c>
+      <x:c r="H17" s="10" t="n">
+        <x:v>0.39</x:v>
+      </x:c>
+      <x:c r="I17" s="6" t="n">
+        <x:v>0.372</x:v>
+      </x:c>
+      <x:c r="J17" s="6" t="n">
+        <x:v>0.396</x:v>
+      </x:c>
+      <x:c r="K17" s="6" t="n">
         <x:v>0.373</x:v>
       </x:c>
-      <x:c r="F17" s="6" t="n">
-        <x:v>0.394</x:v>
-      </x:c>
-      <x:c r="G17" s="6" t="n">
-        <x:v>0.38</x:v>
-      </x:c>
-      <x:c r="H17" s="6" t="n">
-        <x:v>0.403</x:v>
-      </x:c>
-      <x:c r="I17" s="6" t="n">
-        <x:v>0.353</x:v>
-      </x:c>
-      <x:c r="J17" s="6" t="n">
-        <x:v>0.39</x:v>
-      </x:c>
-      <x:c r="K17" s="6" t="n">
-        <x:v>0.372</x:v>
-      </x:c>
       <x:c r="L17" s="6" t="n">
-        <x:v>0.396</x:v>
-      </x:c>
-      <x:c r="M17" s="8" t="n">
-        <x:v>0.318</x:v>
-      </x:c>
-      <x:c r="N17" s="8" t="n">
-        <x:v>0.36</x:v>
+        <x:v>0.399</x:v>
+      </x:c>
+      <x:c r="M17" s="6" t="n">
+        <x:v>0.383</x:v>
+      </x:c>
+      <x:c r="N17" s="6" t="n">
+        <x:v>0.406</x:v>
       </x:c>
       <x:c r="O17" s="6" t="n">
-        <x:v>0.383</x:v>
+        <x:v>0.384</x:v>
       </x:c>
       <x:c r="P17" s="6" t="n">
+        <x:v>0.405</x:v>
+      </x:c>
+      <x:c r="Q17" s="6" t="n">
+        <x:v>0.386</x:v>
+      </x:c>
+      <x:c r="R17" s="6" t="n">
         <x:v>0.406</x:v>
       </x:c>
-      <x:c r="Q17" s="6" t="n">
-        <x:v>0.384</x:v>
-      </x:c>
-      <x:c r="R17" s="6" t="n">
-        <x:v>0.405</x:v>
-      </x:c>
       <x:c r="S17" s="6" t="n">
-        <x:v>0.386</x:v>
+        <x:v>0.414</x:v>
       </x:c>
       <x:c r="T17" s="6" t="n">
-        <x:v>0.406</x:v>
+        <x:v>0.427</x:v>
       </x:c>
       <x:c r="U17" s="6" t="n">
-        <x:v>0.558</x:v>
+        <x:v>0.436</x:v>
       </x:c>
       <x:c r="V17" s="6" t="n">
-        <x:v>0.515</x:v>
-      </x:c>
-      <x:c r="W17" s="6" t="n">
-        <x:v>0.436</x:v>
-      </x:c>
-      <x:c r="X17" s="6" t="n">
         <x:v>0.449</x:v>
       </x:c>
     </x:row>
@@ -1575,70 +1381,56 @@
       <x:c r="B18" s="4" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C18" s="9" t="n">
+      <x:c r="C18" s="8" t="n">
         <x:v>0.167</x:v>
       </x:c>
-      <x:c r="D18" s="6" t="n">
+      <x:c r="D18" s="8" t="n">
         <x:v>0.249</x:v>
       </x:c>
-      <x:c r="E18" s="9" t="n">
-        <x:v>0.167</x:v>
-      </x:c>
-      <x:c r="F18" s="8" t="n">
-        <x:v>0.245</x:v>
+      <x:c r="E18" s="6" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="F18" s="6" t="n">
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="G18" s="6" t="n">
+        <x:v>0.173</x:v>
+      </x:c>
+      <x:c r="H18" s="6" t="n">
+        <x:v>0.257</x:v>
+      </x:c>
+      <x:c r="I18" s="10" t="n">
+        <x:v>0.172</x:v>
+      </x:c>
+      <x:c r="J18" s="10" t="n">
+        <x:v>0.255</x:v>
+      </x:c>
+      <x:c r="K18" s="6"/>
+      <x:c r="L18" s="6"/>
+      <x:c r="M18" s="6" t="n">
         <x:v>0.18</x:v>
       </x:c>
-      <x:c r="H18" s="6" t="n">
-        <x:v>0.26</x:v>
-      </x:c>
-      <x:c r="I18" s="6" t="n">
-        <x:v>0.173</x:v>
-      </x:c>
-      <x:c r="J18" s="6" t="n">
-        <x:v>0.257</x:v>
-      </x:c>
-      <x:c r="K18" s="6" t="n">
-        <x:v>0.172</x:v>
-      </x:c>
-      <x:c r="L18" s="6" t="n">
-        <x:v>0.255</x:v>
-      </x:c>
-      <x:c r="M18" s="8" t="n">
-        <x:v>0.164</x:v>
-      </x:c>
-      <x:c r="N18" s="9" t="n">
-        <x:v>0.248</x:v>
+      <x:c r="N18" s="6" t="n">
+        <x:v>0.264</x:v>
       </x:c>
       <x:c r="O18" s="6" t="n">
-        <x:v>0.18</x:v>
+        <x:v>0.175</x:v>
       </x:c>
       <x:c r="P18" s="6" t="n">
-        <x:v>0.264</x:v>
+        <x:v>0.256</x:v>
       </x:c>
       <x:c r="Q18" s="6" t="n">
         <x:v>0.175</x:v>
       </x:c>
       <x:c r="R18" s="6" t="n">
-        <x:v>0.256</x:v>
-      </x:c>
-      <x:c r="S18" s="6" t="n">
-        <x:v>0.175</x:v>
-      </x:c>
-      <x:c r="T18" s="6" t="n">
         <x:v>0.259</x:v>
       </x:c>
+      <x:c r="S18" s="6"/>
+      <x:c r="T18" s="6"/>
       <x:c r="U18" s="6" t="n">
-        <x:v>0.193</x:v>
+        <x:v>0.203</x:v>
       </x:c>
       <x:c r="V18" s="6" t="n">
-        <x:v>0.292</x:v>
-      </x:c>
-      <x:c r="W18" s="6" t="n">
-        <x:v>0.203</x:v>
-      </x:c>
-      <x:c r="X18" s="6" t="n">
         <x:v>0.287</x:v>
       </x:c>
     </x:row>
@@ -1649,70 +1441,56 @@
       <x:c r="B19" s="4" t="n">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="C19" s="9" t="n">
+      <x:c r="C19" s="8" t="n">
         <x:v>0.231</x:v>
       </x:c>
-      <x:c r="D19" s="9" t="n">
+      <x:c r="D19" s="8" t="n">
         <x:v>0.291</x:v>
       </x:c>
       <x:c r="E19" s="6" t="n">
-        <x:v>0.233</x:v>
-      </x:c>
-      <x:c r="F19" s="8" t="n">
-        <x:v>0.29</x:v>
+        <x:v>0.242</x:v>
+      </x:c>
+      <x:c r="F19" s="6" t="n">
+        <x:v>0.302</x:v>
       </x:c>
       <x:c r="G19" s="6" t="n">
-        <x:v>0.242</x:v>
-      </x:c>
-      <x:c r="H19" s="6" t="n">
+        <x:v>0.238</x:v>
+      </x:c>
+      <x:c r="H19" s="10" t="n">
+        <x:v>0.299</x:v>
+      </x:c>
+      <x:c r="I19" s="10" t="n">
+        <x:v>0.237</x:v>
+      </x:c>
+      <x:c r="J19" s="10" t="n">
+        <x:v>0.299</x:v>
+      </x:c>
+      <x:c r="K19" s="6"/>
+      <x:c r="L19" s="6"/>
+      <x:c r="M19" s="6" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="N19" s="6" t="n">
+        <x:v>0.309</x:v>
+      </x:c>
+      <x:c r="O19" s="6" t="n">
+        <x:v>0.243</x:v>
+      </x:c>
+      <x:c r="P19" s="6" t="n">
+        <x:v>0.303</x:v>
+      </x:c>
+      <x:c r="Q19" s="6" t="n">
+        <x:v>0.241</x:v>
+      </x:c>
+      <x:c r="R19" s="6" t="n">
         <x:v>0.302</x:v>
       </x:c>
-      <x:c r="I19" s="6" t="n">
-        <x:v>0.238</x:v>
-      </x:c>
-      <x:c r="J19" s="6" t="n">
-        <x:v>0.299</x:v>
-      </x:c>
-      <x:c r="K19" s="6" t="n">
-        <x:v>0.237</x:v>
-      </x:c>
-      <x:c r="L19" s="6" t="n">
-        <x:v>0.299</x:v>
-      </x:c>
-      <x:c r="M19" s="8" t="n">
-        <x:v>0.23</x:v>
-      </x:c>
-      <x:c r="N19" s="9" t="n">
-        <x:v>0.291</x:v>
-      </x:c>
-      <x:c r="O19" s="6" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="P19" s="6" t="n">
-        <x:v>0.309</x:v>
-      </x:c>
-      <x:c r="Q19" s="6" t="n">
-        <x:v>0.243</x:v>
-      </x:c>
-      <x:c r="R19" s="6" t="n">
-        <x:v>0.303</x:v>
-      </x:c>
-      <x:c r="S19" s="6" t="n">
-        <x:v>0.241</x:v>
-      </x:c>
-      <x:c r="T19" s="6" t="n">
-        <x:v>0.302</x:v>
-      </x:c>
+      <x:c r="S19" s="6"/>
+      <x:c r="T19" s="6"/>
       <x:c r="U19" s="6" t="n">
-        <x:v>0.284</x:v>
+        <x:v>0.269</x:v>
       </x:c>
       <x:c r="V19" s="6" t="n">
-        <x:v>0.362</x:v>
-      </x:c>
-      <x:c r="W19" s="6" t="n">
-        <x:v>0.269</x:v>
-      </x:c>
-      <x:c r="X19" s="6" t="n">
         <x:v>0.328</x:v>
       </x:c>
     </x:row>
@@ -1726,67 +1504,53 @@
       <x:c r="C20" s="8" t="n">
         <x:v>0.291</x:v>
       </x:c>
-      <x:c r="D20" s="6" t="n">
+      <x:c r="D20" s="8" t="n">
         <x:v>0.332</x:v>
       </x:c>
       <x:c r="E20" s="6" t="n">
-        <x:v>0.293</x:v>
-      </x:c>
-      <x:c r="F20" s="8" t="n">
-        <x:v>0.328</x:v>
-      </x:c>
-      <x:c r="G20" s="6" t="n">
         <x:v>0.308</x:v>
       </x:c>
-      <x:c r="H20" s="6" t="n">
+      <x:c r="F20" s="6" t="n">
         <x:v>0.345</x:v>
       </x:c>
+      <x:c r="G20" s="10" t="n">
+        <x:v>0.296</x:v>
+      </x:c>
+      <x:c r="H20" s="10" t="n">
+        <x:v>0.338</x:v>
+      </x:c>
       <x:c r="I20" s="6" t="n">
-        <x:v>0.296</x:v>
+        <x:v>0.299</x:v>
       </x:c>
       <x:c r="J20" s="6" t="n">
-        <x:v>0.338</x:v>
-      </x:c>
-      <x:c r="K20" s="6" t="n">
-        <x:v>0.299</x:v>
-      </x:c>
-      <x:c r="L20" s="6" t="n">
         <x:v>0.398</x:v>
       </x:c>
-      <x:c r="M20" s="9" t="n">
-        <x:v>0.292</x:v>
-      </x:c>
-      <x:c r="N20" s="9" t="n">
-        <x:v>0.331</x:v>
+      <x:c r="K20" s="6"/>
+      <x:c r="L20" s="6"/>
+      <x:c r="M20" s="6" t="n">
+        <x:v>0.311</x:v>
+      </x:c>
+      <x:c r="N20" s="6" t="n">
+        <x:v>0.348</x:v>
       </x:c>
       <x:c r="O20" s="6" t="n">
-        <x:v>0.311</x:v>
+        <x:v>0.303</x:v>
       </x:c>
       <x:c r="P20" s="6" t="n">
-        <x:v>0.348</x:v>
+        <x:v>0.341</x:v>
       </x:c>
       <x:c r="Q20" s="6" t="n">
-        <x:v>0.303</x:v>
+        <x:v>0.305</x:v>
       </x:c>
       <x:c r="R20" s="6" t="n">
-        <x:v>0.341</x:v>
-      </x:c>
-      <x:c r="S20" s="6" t="n">
-        <x:v>0.305</x:v>
-      </x:c>
-      <x:c r="T20" s="6" t="n">
         <x:v>0.343</x:v>
       </x:c>
+      <x:c r="S20" s="6"/>
+      <x:c r="T20" s="6"/>
       <x:c r="U20" s="6" t="n">
-        <x:v>0.369</x:v>
+        <x:v>0.325</x:v>
       </x:c>
       <x:c r="V20" s="6" t="n">
-        <x:v>0.427</x:v>
-      </x:c>
-      <x:c r="W20" s="6" t="n">
-        <x:v>0.325</x:v>
-      </x:c>
-      <x:c r="X20" s="6" t="n">
         <x:v>0.366</x:v>
       </x:c>
     </x:row>
@@ -1797,70 +1561,56 @@
       <x:c r="B21" s="4" t="n">
         <x:v>720</x:v>
       </x:c>
-      <x:c r="C21" s="9" t="n">
+      <x:c r="C21" s="8" t="n">
         <x:v>0.384</x:v>
       </x:c>
-      <x:c r="D21" s="6" t="n">
+      <x:c r="D21" s="8" t="n">
         <x:v>0.389</x:v>
       </x:c>
       <x:c r="E21" s="6" t="n">
-        <x:v>0.39</x:v>
-      </x:c>
-      <x:c r="F21" s="9" t="n">
-        <x:v>0.386</x:v>
-      </x:c>
-      <x:c r="G21" s="6" t="n">
         <x:v>0.405</x:v>
       </x:c>
+      <x:c r="F21" s="6" t="n">
+        <x:v>0.401</x:v>
+      </x:c>
+      <x:c r="G21" s="10" t="n">
+        <x:v>0.393</x:v>
+      </x:c>
       <x:c r="H21" s="6" t="n">
-        <x:v>0.401</x:v>
+        <x:v>0.395</x:v>
       </x:c>
       <x:c r="I21" s="6" t="n">
-        <x:v>0.393</x:v>
-      </x:c>
-      <x:c r="J21" s="6" t="n">
-        <x:v>0.395</x:v>
-      </x:c>
-      <x:c r="K21" s="6" t="n">
         <x:v>0.397</x:v>
       </x:c>
-      <x:c r="L21" s="6" t="n">
+      <x:c r="J21" s="10" t="n">
         <x:v>0.394</x:v>
       </x:c>
-      <x:c r="M21" s="8" t="n">
-        <x:v>0.381</x:v>
-      </x:c>
-      <x:c r="N21" s="8" t="n">
-        <x:v>0.383</x:v>
+      <x:c r="K21" s="6"/>
+      <x:c r="L21" s="6"/>
+      <x:c r="M21" s="6" t="n">
+        <x:v>0.412</x:v>
+      </x:c>
+      <x:c r="N21" s="6" t="n">
+        <x:v>0.407</x:v>
       </x:c>
       <x:c r="O21" s="6" t="n">
-        <x:v>0.412</x:v>
+        <x:v>0.396</x:v>
       </x:c>
       <x:c r="P21" s="6" t="n">
-        <x:v>0.407</x:v>
+        <x:v>0.399</x:v>
       </x:c>
       <x:c r="Q21" s="6" t="n">
-        <x:v>0.396</x:v>
+        <x:v>0.402</x:v>
       </x:c>
       <x:c r="R21" s="6" t="n">
-        <x:v>0.399</x:v>
-      </x:c>
-      <x:c r="S21" s="6" t="n">
-        <x:v>0.402</x:v>
-      </x:c>
-      <x:c r="T21" s="6" t="n">
         <x:v>0.4</x:v>
       </x:c>
+      <x:c r="S21" s="6"/>
+      <x:c r="T21" s="6"/>
       <x:c r="U21" s="6" t="n">
-        <x:v>0.554</x:v>
+        <x:v>0.421</x:v>
       </x:c>
       <x:c r="V21" s="6" t="n">
-        <x:v>0.522</x:v>
-      </x:c>
-      <x:c r="W21" s="6" t="n">
-        <x:v>0.421</x:v>
-      </x:c>
-      <x:c r="X21" s="6" t="n">
         <x:v>0.415</x:v>
       </x:c>
     </x:row>
@@ -1871,70 +1621,64 @@
       <x:c r="B22" s="4" t="str">
         <x:v>AVG</x:v>
       </x:c>
-      <x:c r="C22" s="9" t="n">
+      <x:c r="C22" s="8" t="n">
         <x:v>0.268</x:v>
       </x:c>
-      <x:c r="D22" s="6" t="n">
+      <x:c r="D22" s="8" t="n">
         <x:v>0.315</x:v>
       </x:c>
       <x:c r="E22" s="6" t="n">
-        <x:v>0.27</x:v>
-      </x:c>
-      <x:c r="F22" s="8" t="n">
-        <x:v>0.312</x:v>
-      </x:c>
-      <x:c r="G22" s="6" t="n">
         <x:v>0.283</x:v>
       </x:c>
-      <x:c r="H22" s="6" t="n">
+      <x:c r="F22" s="6" t="n">
         <x:v>0.327</x:v>
       </x:c>
+      <x:c r="G22" s="10" t="n">
+        <x:v>0.275</x:v>
+      </x:c>
+      <x:c r="H22" s="10" t="n">
+        <x:v>0.322</x:v>
+      </x:c>
       <x:c r="I22" s="6" t="n">
-        <x:v>0.275</x:v>
+        <x:v>0.276</x:v>
       </x:c>
       <x:c r="J22" s="6" t="n">
-        <x:v>0.322</x:v>
+        <x:v>0.336</x:v>
       </x:c>
       <x:c r="K22" s="6" t="n">
-        <x:v>0.276</x:v>
+        <x:v>0.281</x:v>
       </x:c>
       <x:c r="L22" s="6" t="n">
-        <x:v>0.336</x:v>
-      </x:c>
-      <x:c r="M22" s="8" t="n">
-        <x:v>0.266</x:v>
-      </x:c>
-      <x:c r="N22" s="9" t="n">
-        <x:v>0.313</x:v>
+        <x:v>0.325</x:v>
+      </x:c>
+      <x:c r="M22" s="6" t="n">
+        <x:v>0.288</x:v>
+      </x:c>
+      <x:c r="N22" s="6" t="n">
+        <x:v>0.332</x:v>
       </x:c>
       <x:c r="O22" s="6" t="n">
-        <x:v>0.288</x:v>
+        <x:v>0.279</x:v>
       </x:c>
       <x:c r="P22" s="6" t="n">
-        <x:v>0.332</x:v>
+        <x:v>0.324</x:v>
       </x:c>
       <x:c r="Q22" s="6" t="n">
-        <x:v>0.279</x:v>
+        <x:v>0.28</x:v>
       </x:c>
       <x:c r="R22" s="6" t="n">
-        <x:v>0.324</x:v>
+        <x:v>0.326</x:v>
       </x:c>
       <x:c r="S22" s="6" t="n">
-        <x:v>0.28</x:v>
+        <x:v>0.291</x:v>
       </x:c>
       <x:c r="T22" s="6" t="n">
-        <x:v>0.326</x:v>
+        <x:v>0.333</x:v>
       </x:c>
       <x:c r="U22" s="6" t="n">
-        <x:v>0.35</x:v>
+        <x:v>0.304</x:v>
       </x:c>
       <x:c r="V22" s="6" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="W22" s="6" t="n">
-        <x:v>0.304</x:v>
-      </x:c>
-      <x:c r="X22" s="6" t="n">
         <x:v>0.349</x:v>
       </x:c>
     </x:row>
@@ -1945,70 +1689,56 @@
       <x:c r="B23" s="4" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C23" s="9" t="n">
+      <x:c r="C23" s="8" t="n">
         <x:v>0.131</x:v>
       </x:c>
-      <x:c r="D23" s="9" t="n">
+      <x:c r="D23" s="8" t="n">
         <x:v>0.226</x:v>
       </x:c>
-      <x:c r="E23" s="8" t="n">
-        <x:v>0.13</x:v>
-      </x:c>
-      <x:c r="F23" s="8" t="n">
-        <x:v>0.219</x:v>
+      <x:c r="E23" s="10" t="n">
+        <x:v>0.135</x:v>
+      </x:c>
+      <x:c r="F23" s="10" t="n">
+        <x:v>0.229</x:v>
       </x:c>
       <x:c r="G23" s="6" t="n">
-        <x:v>0.135</x:v>
+        <x:v>0.141</x:v>
       </x:c>
       <x:c r="H23" s="6" t="n">
-        <x:v>0.229</x:v>
+        <x:v>0.235</x:v>
       </x:c>
       <x:c r="I23" s="6" t="n">
-        <x:v>0.141</x:v>
+        <x:v>0.151</x:v>
       </x:c>
       <x:c r="J23" s="6" t="n">
-        <x:v>0.235</x:v>
-      </x:c>
-      <x:c r="K23" s="6" t="n">
-        <x:v>0.151</x:v>
-      </x:c>
-      <x:c r="L23" s="6" t="n">
         <x:v>0.245</x:v>
       </x:c>
+      <x:c r="K23" s="6"/>
+      <x:c r="L23" s="6"/>
       <x:c r="M23" s="6" t="n">
-        <x:v>0.159</x:v>
+        <x:v>0.148</x:v>
       </x:c>
       <x:c r="N23" s="6" t="n">
-        <x:v>0.244</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="O23" s="6" t="n">
-        <x:v>0.148</x:v>
+        <x:v>0.154</x:v>
       </x:c>
       <x:c r="P23" s="6" t="n">
-        <x:v>0.24</x:v>
+        <x:v>0.246</x:v>
       </x:c>
       <x:c r="Q23" s="6" t="n">
-        <x:v>0.154</x:v>
+        <x:v>0.181</x:v>
       </x:c>
       <x:c r="R23" s="6" t="n">
-        <x:v>0.246</x:v>
-      </x:c>
-      <x:c r="S23" s="6" t="n">
-        <x:v>0.181</x:v>
-      </x:c>
-      <x:c r="T23" s="6" t="n">
         <x:v>0.27</x:v>
       </x:c>
+      <x:c r="S23" s="6"/>
+      <x:c r="T23" s="6"/>
       <x:c r="U23" s="6" t="n">
-        <x:v>0.197</x:v>
+        <x:v>0.193</x:v>
       </x:c>
       <x:c r="V23" s="6" t="n">
-        <x:v>0.282</x:v>
-      </x:c>
-      <x:c r="W23" s="6" t="n">
-        <x:v>0.193</x:v>
-      </x:c>
-      <x:c r="X23" s="6" t="n">
         <x:v>0.308</x:v>
       </x:c>
     </x:row>
@@ -2022,67 +1752,53 @@
       <x:c r="C24" s="8" t="n">
         <x:v>0.141</x:v>
       </x:c>
-      <x:c r="D24" s="9" t="n">
+      <x:c r="D24" s="8" t="n">
         <x:v>0.239</x:v>
       </x:c>
-      <x:c r="E24" s="9" t="n">
-        <x:v>0.15</x:v>
-      </x:c>
-      <x:c r="F24" s="8" t="n">
-        <x:v>0.237</x:v>
-      </x:c>
-      <x:c r="G24" s="6" t="n">
+      <x:c r="E24" s="10" t="n">
         <x:v>0.151</x:v>
       </x:c>
+      <x:c r="F24" s="10" t="n">
+        <x:v>0.246</x:v>
+      </x:c>
+      <x:c r="G24" s="10" t="n">
+        <x:v>0.151</x:v>
+      </x:c>
       <x:c r="H24" s="6" t="n">
-        <x:v>0.246</x:v>
+        <x:v>0.247</x:v>
       </x:c>
       <x:c r="I24" s="6" t="n">
-        <x:v>0.151</x:v>
+        <x:v>0.163</x:v>
       </x:c>
       <x:c r="J24" s="6" t="n">
-        <x:v>0.247</x:v>
-      </x:c>
-      <x:c r="K24" s="6" t="n">
-        <x:v>0.163</x:v>
-      </x:c>
-      <x:c r="L24" s="6" t="n">
         <x:v>0.256</x:v>
       </x:c>
+      <x:c r="K24" s="6"/>
+      <x:c r="L24" s="6"/>
       <x:c r="M24" s="6" t="n">
-        <x:v>0.16</x:v>
+        <x:v>0.162</x:v>
       </x:c>
       <x:c r="N24" s="6" t="n">
-        <x:v>0.248</x:v>
+        <x:v>0.253</x:v>
       </x:c>
       <x:c r="O24" s="6" t="n">
-        <x:v>0.162</x:v>
+        <x:v>0.168</x:v>
       </x:c>
       <x:c r="P24" s="6" t="n">
-        <x:v>0.253</x:v>
+        <x:v>0.258</x:v>
       </x:c>
       <x:c r="Q24" s="6" t="n">
-        <x:v>0.168</x:v>
+        <x:v>0.188</x:v>
       </x:c>
       <x:c r="R24" s="6" t="n">
-        <x:v>0.258</x:v>
-      </x:c>
-      <x:c r="S24" s="6" t="n">
-        <x:v>0.188</x:v>
-      </x:c>
-      <x:c r="T24" s="6" t="n">
         <x:v>0.274</x:v>
       </x:c>
+      <x:c r="S24" s="6"/>
+      <x:c r="T24" s="6"/>
       <x:c r="U24" s="6" t="n">
-        <x:v>0.196</x:v>
+        <x:v>0.201</x:v>
       </x:c>
       <x:c r="V24" s="6" t="n">
-        <x:v>0.285</x:v>
-      </x:c>
-      <x:c r="W24" s="6" t="n">
-        <x:v>0.201</x:v>
-      </x:c>
-      <x:c r="X24" s="6" t="n">
         <x:v>0.315</x:v>
       </x:c>
     </x:row>
@@ -2096,67 +1812,53 @@
       <x:c r="C25" s="8" t="n">
         <x:v>0.163</x:v>
       </x:c>
-      <x:c r="D25" s="9" t="n">
+      <x:c r="D25" s="8" t="n">
         <x:v>0.259</x:v>
       </x:c>
-      <x:c r="E25" s="9" t="n">
-        <x:v>0.165</x:v>
-      </x:c>
-      <x:c r="F25" s="8" t="n">
-        <x:v>0.255</x:v>
+      <x:c r="E25" s="10" t="n">
+        <x:v>0.172</x:v>
+      </x:c>
+      <x:c r="F25" s="6" t="n">
+        <x:v>0.268</x:v>
       </x:c>
       <x:c r="G25" s="6" t="n">
-        <x:v>0.172</x:v>
-      </x:c>
-      <x:c r="H25" s="6" t="n">
-        <x:v>0.268</x:v>
+        <x:v>0.173</x:v>
+      </x:c>
+      <x:c r="H25" s="10" t="n">
+        <x:v>0.267</x:v>
       </x:c>
       <x:c r="I25" s="6" t="n">
-        <x:v>0.173</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="J25" s="6" t="n">
-        <x:v>0.267</x:v>
-      </x:c>
-      <x:c r="K25" s="6" t="n">
-        <x:v>0.18</x:v>
-      </x:c>
-      <x:c r="L25" s="6" t="n">
         <x:v>0.274</x:v>
       </x:c>
+      <x:c r="K25" s="6"/>
+      <x:c r="L25" s="6"/>
       <x:c r="M25" s="6" t="n">
-        <x:v>0.182</x:v>
+        <x:v>0.178</x:v>
       </x:c>
       <x:c r="N25" s="6" t="n">
-        <x:v>0.267</x:v>
+        <x:v>0.269</x:v>
       </x:c>
       <x:c r="O25" s="6" t="n">
-        <x:v>0.178</x:v>
+        <x:v>0.185</x:v>
       </x:c>
       <x:c r="P25" s="6" t="n">
-        <x:v>0.269</x:v>
+        <x:v>0.275</x:v>
       </x:c>
       <x:c r="Q25" s="6" t="n">
-        <x:v>0.185</x:v>
+        <x:v>0.204</x:v>
       </x:c>
       <x:c r="R25" s="6" t="n">
-        <x:v>0.275</x:v>
-      </x:c>
-      <x:c r="S25" s="6" t="n">
-        <x:v>0.204</x:v>
-      </x:c>
-      <x:c r="T25" s="6" t="n">
         <x:v>0.293</x:v>
       </x:c>
+      <x:c r="S25" s="6"/>
+      <x:c r="T25" s="6"/>
       <x:c r="U25" s="6" t="n">
-        <x:v>0.209</x:v>
+        <x:v>0.214</x:v>
       </x:c>
       <x:c r="V25" s="6" t="n">
-        <x:v>0.301</x:v>
-      </x:c>
-      <x:c r="W25" s="6" t="n">
-        <x:v>0.214</x:v>
-      </x:c>
-      <x:c r="X25" s="6" t="n">
         <x:v>0.329</x:v>
       </x:c>
     </x:row>
@@ -2167,70 +1869,56 @@
       <x:c r="B26" s="4" t="n">
         <x:v>720</x:v>
       </x:c>
-      <x:c r="C26" s="9" t="n">
+      <x:c r="C26" s="8" t="n">
         <x:v>0.188</x:v>
       </x:c>
-      <x:c r="D26" s="9" t="n">
+      <x:c r="D26" s="8" t="n">
         <x:v>0.283</x:v>
       </x:c>
-      <x:c r="E26" s="8" t="n">
-        <x:v>0.187</x:v>
-      </x:c>
-      <x:c r="F26" s="8" t="n">
-        <x:v>0.274</x:v>
-      </x:c>
-      <x:c r="G26" s="6" t="n">
+      <x:c r="E26" s="6" t="n">
         <x:v>0.204</x:v>
       </x:c>
-      <x:c r="H26" s="6" t="n">
+      <x:c r="F26" s="6" t="n">
         <x:v>0.294</x:v>
       </x:c>
+      <x:c r="G26" s="10" t="n">
+        <x:v>0.201</x:v>
+      </x:c>
+      <x:c r="H26" s="10" t="n">
+        <x:v>0.293</x:v>
+      </x:c>
       <x:c r="I26" s="6" t="n">
-        <x:v>0.201</x:v>
+        <x:v>0.224</x:v>
       </x:c>
       <x:c r="J26" s="6" t="n">
-        <x:v>0.293</x:v>
-      </x:c>
-      <x:c r="K26" s="6" t="n">
-        <x:v>0.224</x:v>
-      </x:c>
-      <x:c r="L26" s="6" t="n">
         <x:v>0.311</x:v>
       </x:c>
+      <x:c r="K26" s="6"/>
+      <x:c r="L26" s="6"/>
       <x:c r="M26" s="6" t="n">
-        <x:v>0.216</x:v>
+        <x:v>0.225</x:v>
       </x:c>
       <x:c r="N26" s="6" t="n">
-        <x:v>0.298</x:v>
+        <x:v>0.317</x:v>
       </x:c>
       <x:c r="O26" s="6" t="n">
         <x:v>0.225</x:v>
       </x:c>
       <x:c r="P26" s="6" t="n">
-        <x:v>0.317</x:v>
+        <x:v>0.312</x:v>
       </x:c>
       <x:c r="Q26" s="6" t="n">
-        <x:v>0.225</x:v>
+        <x:v>0.246</x:v>
       </x:c>
       <x:c r="R26" s="6" t="n">
-        <x:v>0.312</x:v>
-      </x:c>
-      <x:c r="S26" s="6" t="n">
+        <x:v>0.324</x:v>
+      </x:c>
+      <x:c r="S26" s="6"/>
+      <x:c r="T26" s="6"/>
+      <x:c r="U26" s="6" t="n">
         <x:v>0.246</x:v>
       </x:c>
-      <x:c r="T26" s="6" t="n">
-        <x:v>0.324</x:v>
-      </x:c>
-      <x:c r="U26" s="6" t="n">
-        <x:v>0.245</x:v>
-      </x:c>
       <x:c r="V26" s="6" t="n">
-        <x:v>0.333</x:v>
-      </x:c>
-      <x:c r="W26" s="6" t="n">
-        <x:v>0.246</x:v>
-      </x:c>
-      <x:c r="X26" s="6" t="n">
         <x:v>0.355</x:v>
       </x:c>
     </x:row>
@@ -2244,67 +1932,61 @@
       <x:c r="C27" s="8" t="n">
         <x:v>0.156</x:v>
       </x:c>
-      <x:c r="D27" s="9" t="n">
+      <x:c r="D27" s="8" t="n">
         <x:v>0.252</x:v>
       </x:c>
-      <x:c r="E27" s="9" t="n">
-        <x:v>0.158</x:v>
-      </x:c>
-      <x:c r="F27" s="8" t="n">
-        <x:v>0.246</x:v>
+      <x:c r="E27" s="10" t="n">
+        <x:v>0.165</x:v>
+      </x:c>
+      <x:c r="F27" s="10" t="n">
+        <x:v>0.259</x:v>
       </x:c>
       <x:c r="G27" s="6" t="n">
-        <x:v>0.165</x:v>
+        <x:v>0.166</x:v>
       </x:c>
       <x:c r="H27" s="6" t="n">
-        <x:v>0.259</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I27" s="6" t="n">
+        <x:v>0.179</x:v>
+      </x:c>
+      <x:c r="J27" s="6" t="n">
+        <x:v>0.271</x:v>
+      </x:c>
+      <x:c r="K27" s="6" t="n">
         <x:v>0.166</x:v>
       </x:c>
-      <x:c r="J27" s="6" t="n">
-        <x:v>0.26</x:v>
-      </x:c>
-      <x:c r="K27" s="6" t="n">
-        <x:v>0.179</x:v>
-      </x:c>
       <x:c r="L27" s="6" t="n">
-        <x:v>0.271</x:v>
+        <x:v>0.263</x:v>
       </x:c>
       <x:c r="M27" s="6" t="n">
-        <x:v>0.179</x:v>
+        <x:v>0.178</x:v>
       </x:c>
       <x:c r="N27" s="6" t="n">
-        <x:v>0.264</x:v>
+        <x:v>0.269</x:v>
       </x:c>
       <x:c r="O27" s="6" t="n">
-        <x:v>0.178</x:v>
+        <x:v>0.183</x:v>
       </x:c>
       <x:c r="P27" s="6" t="n">
-        <x:v>0.269</x:v>
+        <x:v>0.272</x:v>
       </x:c>
       <x:c r="Q27" s="6" t="n">
-        <x:v>0.183</x:v>
+        <x:v>0.204</x:v>
       </x:c>
       <x:c r="R27" s="6" t="n">
-        <x:v>0.272</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="S27" s="6" t="n">
-        <x:v>0.204</x:v>
+        <x:v>0.192</x:v>
       </x:c>
       <x:c r="T27" s="6" t="n">
-        <x:v>0.29</x:v>
+        <x:v>0.295</x:v>
       </x:c>
       <x:c r="U27" s="6" t="n">
-        <x:v>0.211</x:v>
+        <x:v>0.213</x:v>
       </x:c>
       <x:c r="V27" s="6" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="W27" s="6" t="n">
-        <x:v>0.213</x:v>
-      </x:c>
-      <x:c r="X27" s="6" t="n">
         <x:v>0.326</x:v>
       </x:c>
     </x:row>
@@ -2318,20 +2000,20 @@
       <x:c r="C28" s="8" t="n">
         <x:v>0.15</x:v>
       </x:c>
-      <x:c r="D28" s="9" t="n">
+      <x:c r="D28" s="8" t="n">
         <x:v>0.194</x:v>
       </x:c>
-      <x:c r="E28" s="9" t="n">
-        <x:v>0.153</x:v>
-      </x:c>
-      <x:c r="F28" s="8" t="n">
-        <x:v>0.19</x:v>
+      <x:c r="E28" s="10" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="F28" s="10" t="n">
+        <x:v>0.206</x:v>
       </x:c>
       <x:c r="G28" s="6" t="n">
-        <x:v>0.16</x:v>
+        <x:v>0.162</x:v>
       </x:c>
       <x:c r="H28" s="6" t="n">
-        <x:v>0.206</x:v>
+        <x:v>0.207</x:v>
       </x:c>
       <x:c r="I28" s="6" t="n">
         <x:v>0.162</x:v>
@@ -2339,46 +2021,32 @@
       <x:c r="J28" s="6" t="n">
         <x:v>0.207</x:v>
       </x:c>
-      <x:c r="K28" s="6" t="n">
-        <x:v>0.162</x:v>
-      </x:c>
-      <x:c r="L28" s="6" t="n">
-        <x:v>0.207</x:v>
-      </x:c>
+      <x:c r="K28" s="6"/>
+      <x:c r="L28" s="6"/>
       <x:c r="M28" s="6" t="n">
-        <x:v>0.168</x:v>
+        <x:v>0.174</x:v>
       </x:c>
       <x:c r="N28" s="6" t="n">
-        <x:v>0.203</x:v>
+        <x:v>0.214</x:v>
       </x:c>
       <x:c r="O28" s="6" t="n">
-        <x:v>0.174</x:v>
+        <x:v>0.163</x:v>
       </x:c>
       <x:c r="P28" s="6" t="n">
-        <x:v>0.214</x:v>
+        <x:v>0.209</x:v>
       </x:c>
       <x:c r="Q28" s="6" t="n">
-        <x:v>0.163</x:v>
+        <x:v>0.177</x:v>
       </x:c>
       <x:c r="R28" s="6" t="n">
-        <x:v>0.209</x:v>
-      </x:c>
-      <x:c r="S28" s="6" t="n">
-        <x:v>0.177</x:v>
-      </x:c>
-      <x:c r="T28" s="6" t="n">
         <x:v>0.218</x:v>
       </x:c>
+      <x:c r="S28" s="6"/>
+      <x:c r="T28" s="6"/>
       <x:c r="U28" s="6" t="n">
-        <x:v>0.196</x:v>
+        <x:v>0.217</x:v>
       </x:c>
       <x:c r="V28" s="6" t="n">
-        <x:v>0.255</x:v>
-      </x:c>
-      <x:c r="W28" s="6" t="n">
-        <x:v>0.217</x:v>
-      </x:c>
-      <x:c r="X28" s="6" t="n">
         <x:v>0.296</x:v>
       </x:c>
     </x:row>
@@ -2392,67 +2060,53 @@
       <x:c r="C29" s="8" t="n">
         <x:v>0.199</x:v>
       </x:c>
-      <x:c r="D29" s="9" t="n">
+      <x:c r="D29" s="8" t="n">
         <x:v>0.24</x:v>
       </x:c>
-      <x:c r="E29" s="9" t="n">
-        <x:v>0.204</x:v>
-      </x:c>
-      <x:c r="F29" s="8" t="n">
-        <x:v>0.239</x:v>
-      </x:c>
-      <x:c r="G29" s="6" t="n">
+      <x:c r="E29" s="10" t="n">
         <x:v>0.208</x:v>
       </x:c>
-      <x:c r="H29" s="6" t="n">
+      <x:c r="F29" s="6" t="n">
         <x:v>0.25</x:v>
       </x:c>
+      <x:c r="G29" s="10" t="n">
+        <x:v>0.208</x:v>
+      </x:c>
+      <x:c r="H29" s="10" t="n">
+        <x:v>0.248</x:v>
+      </x:c>
       <x:c r="I29" s="6" t="n">
+        <x:v>0.209</x:v>
+      </x:c>
+      <x:c r="J29" s="6" t="n">
+        <x:v>0.252</x:v>
+      </x:c>
+      <x:c r="K29" s="6"/>
+      <x:c r="L29" s="6"/>
+      <x:c r="M29" s="6" t="n">
+        <x:v>0.221</x:v>
+      </x:c>
+      <x:c r="N29" s="6" t="n">
+        <x:v>0.254</x:v>
+      </x:c>
+      <x:c r="O29" s="10" t="n">
         <x:v>0.208</x:v>
       </x:c>
-      <x:c r="J29" s="6" t="n">
-        <x:v>0.248</x:v>
-      </x:c>
-      <x:c r="K29" s="6" t="n">
-        <x:v>0.209</x:v>
-      </x:c>
-      <x:c r="L29" s="6" t="n">
-        <x:v>0.252</x:v>
-      </x:c>
-      <x:c r="M29" s="6" t="n">
-        <x:v>0.214</x:v>
-      </x:c>
-      <x:c r="N29" s="6" t="n">
-        <x:v>0.245</x:v>
-      </x:c>
-      <x:c r="O29" s="6" t="n">
-        <x:v>0.221</x:v>
-      </x:c>
       <x:c r="P29" s="6" t="n">
-        <x:v>0.254</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="Q29" s="6" t="n">
-        <x:v>0.208</x:v>
+        <x:v>0.225</x:v>
       </x:c>
       <x:c r="R29" s="6" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="S29" s="6" t="n">
-        <x:v>0.225</x:v>
-      </x:c>
-      <x:c r="T29" s="6" t="n">
         <x:v>0.259</x:v>
       </x:c>
+      <x:c r="S29" s="6"/>
+      <x:c r="T29" s="6"/>
       <x:c r="U29" s="6" t="n">
-        <x:v>0.237</x:v>
+        <x:v>0.276</x:v>
       </x:c>
       <x:c r="V29" s="6" t="n">
-        <x:v>0.296</x:v>
-      </x:c>
-      <x:c r="W29" s="6" t="n">
-        <x:v>0.276</x:v>
-      </x:c>
-      <x:c r="X29" s="6" t="n">
         <x:v>0.336</x:v>
       </x:c>
     </x:row>
@@ -2463,70 +2117,56 @@
       <x:c r="B30" s="4" t="n">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="C30" s="9" t="n">
+      <x:c r="C30" s="8" t="n">
         <x:v>0.256</x:v>
       </x:c>
-      <x:c r="D30" s="6" t="n">
+      <x:c r="D30" s="8" t="n">
         <x:v>0.284</x:v>
       </x:c>
       <x:c r="E30" s="6" t="n">
-        <x:v>0.261</x:v>
-      </x:c>
-      <x:c r="F30" s="9" t="n">
-        <x:v>0.282</x:v>
+        <x:v>0.269</x:v>
+      </x:c>
+      <x:c r="F30" s="6" t="n">
+        <x:v>0.296</x:v>
       </x:c>
       <x:c r="G30" s="6" t="n">
-        <x:v>0.269</x:v>
-      </x:c>
-      <x:c r="H30" s="6" t="n">
-        <x:v>0.296</x:v>
+        <x:v>0.263</x:v>
+      </x:c>
+      <x:c r="H30" s="10" t="n">
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I30" s="6" t="n">
         <x:v>0.263</x:v>
       </x:c>
       <x:c r="J30" s="6" t="n">
-        <x:v>0.29</x:v>
-      </x:c>
-      <x:c r="K30" s="6" t="n">
-        <x:v>0.263</x:v>
-      </x:c>
-      <x:c r="L30" s="6" t="n">
         <x:v>0.292</x:v>
       </x:c>
-      <x:c r="M30" s="8" t="n">
-        <x:v>0.236</x:v>
-      </x:c>
-      <x:c r="N30" s="8" t="n">
-        <x:v>0.273</x:v>
-      </x:c>
-      <x:c r="O30" s="6" t="n">
+      <x:c r="K30" s="6"/>
+      <x:c r="L30" s="6"/>
+      <x:c r="M30" s="6" t="n">
         <x:v>0.278</x:v>
       </x:c>
+      <x:c r="N30" s="6" t="n">
+        <x:v>0.296</x:v>
+      </x:c>
+      <x:c r="O30" s="10" t="n">
+        <x:v>0.262</x:v>
+      </x:c>
       <x:c r="P30" s="6" t="n">
-        <x:v>0.296</x:v>
+        <x:v>0.292</x:v>
       </x:c>
       <x:c r="Q30" s="6" t="n">
-        <x:v>0.262</x:v>
+        <x:v>0.278</x:v>
       </x:c>
       <x:c r="R30" s="6" t="n">
-        <x:v>0.292</x:v>
-      </x:c>
-      <x:c r="S30" s="6" t="n">
-        <x:v>0.278</x:v>
-      </x:c>
-      <x:c r="T30" s="6" t="n">
         <x:v>0.297</x:v>
       </x:c>
+      <x:c r="S30" s="6"/>
+      <x:c r="T30" s="6"/>
       <x:c r="U30" s="6" t="n">
-        <x:v>0.283</x:v>
+        <x:v>0.339</x:v>
       </x:c>
       <x:c r="V30" s="6" t="n">
-        <x:v>0.335</x:v>
-      </x:c>
-      <x:c r="W30" s="6" t="n">
-        <x:v>0.339</x:v>
-      </x:c>
-      <x:c r="X30" s="6" t="n">
         <x:v>0.38</x:v>
       </x:c>
     </x:row>
@@ -2537,70 +2177,56 @@
       <x:c r="B31" s="4" t="n">
         <x:v>720</x:v>
       </x:c>
-      <x:c r="C31" s="9" t="n">
+      <x:c r="C31" s="8" t="n">
         <x:v>0.335</x:v>
       </x:c>
-      <x:c r="D31" s="6" t="n">
+      <x:c r="D31" s="10" t="n">
         <x:v>0.338</x:v>
       </x:c>
       <x:c r="E31" s="6" t="n">
-        <x:v>0.342</x:v>
-      </x:c>
-      <x:c r="F31" s="6" t="n">
-        <x:v>0.336</x:v>
-      </x:c>
-      <x:c r="G31" s="6" t="n">
         <x:v>0.343</x:v>
       </x:c>
-      <x:c r="H31" s="9" t="n">
+      <x:c r="F31" s="8" t="n">
         <x:v>0.334</x:v>
       </x:c>
+      <x:c r="G31" s="10" t="n">
+        <x:v>0.34</x:v>
+      </x:c>
+      <x:c r="H31" s="6" t="n">
+        <x:v>0.341</x:v>
+      </x:c>
       <x:c r="I31" s="6" t="n">
-        <x:v>0.34</x:v>
+        <x:v>0.344</x:v>
       </x:c>
       <x:c r="J31" s="6" t="n">
-        <x:v>0.341</x:v>
-      </x:c>
-      <x:c r="K31" s="6" t="n">
         <x:v>0.344</x:v>
       </x:c>
-      <x:c r="L31" s="6" t="n">
-        <x:v>0.344</x:v>
-      </x:c>
-      <x:c r="M31" s="8" t="n">
-        <x:v>0.309</x:v>
-      </x:c>
-      <x:c r="N31" s="8" t="n">
-        <x:v>0.321</x:v>
+      <x:c r="K31" s="6"/>
+      <x:c r="L31" s="6"/>
+      <x:c r="M31" s="6" t="n">
+        <x:v>0.358</x:v>
+      </x:c>
+      <x:c r="N31" s="6" t="n">
+        <x:v>0.347</x:v>
       </x:c>
       <x:c r="O31" s="6" t="n">
-        <x:v>0.358</x:v>
+        <x:v>0.345</x:v>
       </x:c>
       <x:c r="P31" s="6" t="n">
-        <x:v>0.347</x:v>
+        <x:v>0.345</x:v>
       </x:c>
       <x:c r="Q31" s="6" t="n">
-        <x:v>0.345</x:v>
+        <x:v>0.354</x:v>
       </x:c>
       <x:c r="R31" s="6" t="n">
-        <x:v>0.345</x:v>
-      </x:c>
-      <x:c r="S31" s="6" t="n">
-        <x:v>0.354</x:v>
-      </x:c>
-      <x:c r="T31" s="6" t="n">
         <x:v>0.348</x:v>
       </x:c>
+      <x:c r="S31" s="6"/>
+      <x:c r="T31" s="6"/>
       <x:c r="U31" s="6" t="n">
-        <x:v>0.345</x:v>
+        <x:v>0.403</x:v>
       </x:c>
       <x:c r="V31" s="6" t="n">
-        <x:v>0.381</x:v>
-      </x:c>
-      <x:c r="W31" s="6" t="n">
-        <x:v>0.403</x:v>
-      </x:c>
-      <x:c r="X31" s="6" t="n">
         <x:v>0.428</x:v>
       </x:c>
     </x:row>
@@ -2611,70 +2237,64 @@
       <x:c r="B32" s="4" t="str">
         <x:v>AVG</x:v>
       </x:c>
-      <x:c r="C32" s="9" t="n">
+      <x:c r="C32" s="8" t="n">
         <x:v>0.235</x:v>
       </x:c>
-      <x:c r="D32" s="6" t="n">
+      <x:c r="D32" s="8" t="n">
         <x:v>0.264</x:v>
       </x:c>
       <x:c r="E32" s="6" t="n">
-        <x:v>0.24</x:v>
-      </x:c>
-      <x:c r="F32" s="9" t="n">
-        <x:v>0.261</x:v>
-      </x:c>
-      <x:c r="G32" s="6" t="n">
         <x:v>0.245</x:v>
       </x:c>
-      <x:c r="H32" s="6" t="n">
+      <x:c r="F32" s="10" t="n">
         <x:v>0.271</x:v>
       </x:c>
+      <x:c r="G32" s="10" t="n">
+        <x:v>0.243</x:v>
+      </x:c>
+      <x:c r="H32" s="10" t="n">
+        <x:v>0.271</x:v>
+      </x:c>
       <x:c r="I32" s="6" t="n">
-        <x:v>0.243</x:v>
+        <x:v>0.244</x:v>
       </x:c>
       <x:c r="J32" s="6" t="n">
-        <x:v>0.271</x:v>
+        <x:v>0.273</x:v>
       </x:c>
       <x:c r="K32" s="6" t="n">
+        <x:v>0.251</x:v>
+      </x:c>
+      <x:c r="L32" s="6" t="n">
+        <x:v>0.278</x:v>
+      </x:c>
+      <x:c r="M32" s="6" t="n">
+        <x:v>0.257</x:v>
+      </x:c>
+      <x:c r="N32" s="6" t="n">
+        <x:v>0.277</x:v>
+      </x:c>
+      <x:c r="O32" s="6" t="n">
         <x:v>0.244</x:v>
       </x:c>
-      <x:c r="L32" s="6" t="n">
-        <x:v>0.273</x:v>
-      </x:c>
-      <x:c r="M32" s="8" t="n">
-        <x:v>0.231</x:v>
-      </x:c>
-      <x:c r="N32" s="8" t="n">
-        <x:v>0.26</x:v>
-      </x:c>
-      <x:c r="O32" s="6" t="n">
-        <x:v>0.257</x:v>
-      </x:c>
       <x:c r="P32" s="6" t="n">
-        <x:v>0.277</x:v>
+        <x:v>0.274</x:v>
       </x:c>
       <x:c r="Q32" s="6" t="n">
-        <x:v>0.244</x:v>
+        <x:v>0.258</x:v>
       </x:c>
       <x:c r="R32" s="6" t="n">
-        <x:v>0.274</x:v>
+        <x:v>0.28</x:v>
       </x:c>
       <x:c r="S32" s="6" t="n">
-        <x:v>0.258</x:v>
+        <x:v>0.259</x:v>
       </x:c>
       <x:c r="T32" s="6" t="n">
-        <x:v>0.28</x:v>
+        <x:v>0.287</x:v>
       </x:c>
       <x:c r="U32" s="6" t="n">
-        <x:v>0.265</x:v>
+        <x:v>0.308</x:v>
       </x:c>
       <x:c r="V32" s="6" t="n">
-        <x:v>0.316</x:v>
-      </x:c>
-      <x:c r="W32" s="6" t="n">
-        <x:v>0.308</x:v>
-      </x:c>
-      <x:c r="X32" s="6" t="n">
         <x:v>0.36</x:v>
       </x:c>
     </x:row>
@@ -2688,67 +2308,53 @@
       <x:c r="C33" s="8" t="n">
         <x:v>0.16</x:v>
       </x:c>
-      <x:c r="D33" s="6" t="n">
+      <x:c r="D33" s="8" t="n">
         <x:v>0.218</x:v>
       </x:c>
       <x:c r="E33" s="6" t="n">
-        <x:v>0.168</x:v>
-      </x:c>
-      <x:c r="F33" s="8" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="G33" s="6" t="n">
         <x:v>0.192</x:v>
       </x:c>
+      <x:c r="F33" s="10" t="n">
+        <x:v>0.222</x:v>
+      </x:c>
+      <x:c r="G33" s="10" t="n">
+        <x:v>0.163</x:v>
+      </x:c>
       <x:c r="H33" s="6" t="n">
-        <x:v>0.222</x:v>
-      </x:c>
-      <x:c r="I33" s="9" t="n">
-        <x:v>0.163</x:v>
+        <x:v>0.232</x:v>
+      </x:c>
+      <x:c r="I33" s="6" t="n">
+        <x:v>0.183</x:v>
       </x:c>
       <x:c r="J33" s="6" t="n">
-        <x:v>0.232</x:v>
-      </x:c>
-      <x:c r="K33" s="6" t="n">
-        <x:v>0.183</x:v>
-      </x:c>
-      <x:c r="L33" s="6" t="n">
         <x:v>0.234</x:v>
       </x:c>
+      <x:c r="K33" s="6"/>
+      <x:c r="L33" s="6"/>
       <x:c r="M33" s="6" t="n">
-        <x:v>0.201</x:v>
-      </x:c>
-      <x:c r="N33" s="9" t="n">
-        <x:v>0.215</x:v>
+        <x:v>0.203</x:v>
+      </x:c>
+      <x:c r="N33" s="6" t="n">
+        <x:v>0.237</x:v>
       </x:c>
       <x:c r="O33" s="6" t="n">
-        <x:v>0.203</x:v>
+        <x:v>0.189</x:v>
       </x:c>
       <x:c r="P33" s="6" t="n">
-        <x:v>0.237</x:v>
+        <x:v>0.259</x:v>
       </x:c>
       <x:c r="Q33" s="6" t="n">
-        <x:v>0.189</x:v>
+        <x:v>0.225</x:v>
       </x:c>
       <x:c r="R33" s="6" t="n">
-        <x:v>0.259</x:v>
-      </x:c>
-      <x:c r="S33" s="6" t="n">
-        <x:v>0.225</x:v>
-      </x:c>
-      <x:c r="T33" s="6" t="n">
         <x:v>0.27</x:v>
       </x:c>
+      <x:c r="S33" s="6"/>
+      <x:c r="T33" s="6"/>
       <x:c r="U33" s="6" t="n">
-        <x:v>0.29</x:v>
+        <x:v>0.242</x:v>
       </x:c>
       <x:c r="V33" s="6" t="n">
-        <x:v>0.378</x:v>
-      </x:c>
-      <x:c r="W33" s="6" t="n">
-        <x:v>0.242</x:v>
-      </x:c>
-      <x:c r="X33" s="6" t="n">
         <x:v>0.342</x:v>
       </x:c>
     </x:row>
@@ -2762,67 +2368,53 @@
       <x:c r="C34" s="8" t="n">
         <x:v>0.18</x:v>
       </x:c>
-      <x:c r="D34" s="6" t="n">
+      <x:c r="D34" s="8" t="n">
         <x:v>0.246</x:v>
       </x:c>
       <x:c r="E34" s="6" t="n">
-        <x:v>0.19</x:v>
-      </x:c>
-      <x:c r="F34" s="8" t="n">
-        <x:v>0.22</x:v>
-      </x:c>
-      <x:c r="G34" s="6" t="n">
         <x:v>0.23</x:v>
       </x:c>
-      <x:c r="H34" s="6" t="n">
+      <x:c r="F34" s="6" t="n">
         <x:v>0.251</x:v>
       </x:c>
-      <x:c r="I34" s="9" t="n">
+      <x:c r="G34" s="10" t="n">
         <x:v>0.182</x:v>
       </x:c>
+      <x:c r="H34" s="10" t="n">
+        <x:v>0.247</x:v>
+      </x:c>
+      <x:c r="I34" s="6" t="n">
+        <x:v>0.21</x:v>
+      </x:c>
       <x:c r="J34" s="6" t="n">
-        <x:v>0.247</x:v>
-      </x:c>
-      <x:c r="K34" s="6" t="n">
-        <x:v>0.21</x:v>
-      </x:c>
-      <x:c r="L34" s="6" t="n">
         <x:v>0.254</x:v>
       </x:c>
+      <x:c r="K34" s="6"/>
+      <x:c r="L34" s="6"/>
       <x:c r="M34" s="6" t="n">
-        <x:v>0.235</x:v>
-      </x:c>
-      <x:c r="N34" s="9" t="n">
-        <x:v>0.234</x:v>
+        <x:v>0.233</x:v>
+      </x:c>
+      <x:c r="N34" s="6" t="n">
+        <x:v>0.261</x:v>
       </x:c>
       <x:c r="O34" s="6" t="n">
-        <x:v>0.233</x:v>
+        <x:v>0.222</x:v>
       </x:c>
       <x:c r="P34" s="6" t="n">
-        <x:v>0.261</x:v>
+        <x:v>0.283</x:v>
       </x:c>
       <x:c r="Q34" s="6" t="n">
-        <x:v>0.222</x:v>
+        <x:v>0.253</x:v>
       </x:c>
       <x:c r="R34" s="6" t="n">
-        <x:v>0.283</x:v>
-      </x:c>
-      <x:c r="S34" s="6" t="n">
-        <x:v>0.253</x:v>
-      </x:c>
-      <x:c r="T34" s="6" t="n">
         <x:v>0.288</x:v>
       </x:c>
+      <x:c r="S34" s="6"/>
+      <x:c r="T34" s="6"/>
       <x:c r="U34" s="6" t="n">
-        <x:v>0.32</x:v>
+        <x:v>0.285</x:v>
       </x:c>
       <x:c r="V34" s="6" t="n">
-        <x:v>0.398</x:v>
-      </x:c>
-      <x:c r="W34" s="6" t="n">
-        <x:v>0.285</x:v>
-      </x:c>
-      <x:c r="X34" s="6" t="n">
         <x:v>0.38</x:v>
       </x:c>
     </x:row>
@@ -2836,67 +2428,53 @@
       <x:c r="C35" s="8" t="n">
         <x:v>0.19</x:v>
       </x:c>
-      <x:c r="D35" s="6" t="n">
+      <x:c r="D35" s="8" t="n">
         <x:v>0.253</x:v>
       </x:c>
       <x:c r="E35" s="6" t="n">
-        <x:v>0.224</x:v>
-      </x:c>
-      <x:c r="F35" s="8" t="n">
+        <x:v>0.243</x:v>
+      </x:c>
+      <x:c r="F35" s="6" t="n">
+        <x:v>0.263</x:v>
+      </x:c>
+      <x:c r="G35" s="10" t="n">
+        <x:v>0.193</x:v>
+      </x:c>
+      <x:c r="H35" s="10" t="n">
+        <x:v>0.257</x:v>
+      </x:c>
+      <x:c r="I35" s="6" t="n">
+        <x:v>0.217</x:v>
+      </x:c>
+      <x:c r="J35" s="6" t="n">
+        <x:v>0.263</x:v>
+      </x:c>
+      <x:c r="K35" s="6"/>
+      <x:c r="L35" s="6"/>
+      <x:c r="M35" s="6" t="n">
+        <x:v>0.248</x:v>
+      </x:c>
+      <x:c r="N35" s="6" t="n">
+        <x:v>0.273</x:v>
+      </x:c>
+      <x:c r="O35" s="6" t="n">
         <x:v>0.231</x:v>
       </x:c>
-      <x:c r="G35" s="6" t="n">
-        <x:v>0.243</x:v>
-      </x:c>
-      <x:c r="H35" s="6" t="n">
-        <x:v>0.263</x:v>
-      </x:c>
-      <x:c r="I35" s="9" t="n">
-        <x:v>0.193</x:v>
-      </x:c>
-      <x:c r="J35" s="6" t="n">
-        <x:v>0.257</x:v>
-      </x:c>
-      <x:c r="K35" s="6" t="n">
-        <x:v>0.217</x:v>
-      </x:c>
-      <x:c r="L35" s="6" t="n">
-        <x:v>0.263</x:v>
-      </x:c>
-      <x:c r="M35" s="6" t="n">
-        <x:v>0.258</x:v>
-      </x:c>
-      <x:c r="N35" s="9" t="n">
-        <x:v>0.249</x:v>
-      </x:c>
-      <x:c r="O35" s="6" t="n">
-        <x:v>0.248</x:v>
-      </x:c>
       <x:c r="P35" s="6" t="n">
-        <x:v>0.273</x:v>
+        <x:v>0.292</x:v>
       </x:c>
       <x:c r="Q35" s="6" t="n">
-        <x:v>0.231</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="R35" s="6" t="n">
-        <x:v>0.292</x:v>
-      </x:c>
-      <x:c r="S35" s="6" t="n">
-        <x:v>0.27</x:v>
-      </x:c>
-      <x:c r="T35" s="6" t="n">
         <x:v>0.298</x:v>
       </x:c>
+      <x:c r="S35" s="6"/>
+      <x:c r="T35" s="6"/>
       <x:c r="U35" s="6" t="n">
-        <x:v>0.353</x:v>
+        <x:v>0.282</x:v>
       </x:c>
       <x:c r="V35" s="6" t="n">
-        <x:v>0.415</x:v>
-      </x:c>
-      <x:c r="W35" s="6" t="n">
-        <x:v>0.282</x:v>
-      </x:c>
-      <x:c r="X35" s="6" t="n">
         <x:v>0.376</x:v>
       </x:c>
     </x:row>
@@ -2910,67 +2488,53 @@
       <x:c r="C36" s="8" t="n">
         <x:v>0.199</x:v>
       </x:c>
-      <x:c r="D36" s="6" t="n">
+      <x:c r="D36" s="8" t="n">
         <x:v>0.251</x:v>
       </x:c>
-      <x:c r="E36" s="9" t="n">
-        <x:v>0.208</x:v>
-      </x:c>
-      <x:c r="F36" s="8" t="n">
+      <x:c r="E36" s="6" t="n">
         <x:v>0.243</x:v>
       </x:c>
-      <x:c r="G36" s="6" t="n">
-        <x:v>0.243</x:v>
-      </x:c>
-      <x:c r="H36" s="6" t="n">
+      <x:c r="F36" s="6" t="n">
         <x:v>0.265</x:v>
       </x:c>
-      <x:c r="I36" s="8" t="n">
+      <x:c r="G36" s="8" t="n">
         <x:v>0.199</x:v>
       </x:c>
+      <x:c r="H36" s="10" t="n">
+        <x:v>0.252</x:v>
+      </x:c>
+      <x:c r="I36" s="10" t="n">
+        <x:v>0.221</x:v>
+      </x:c>
       <x:c r="J36" s="6" t="n">
-        <x:v>0.252</x:v>
-      </x:c>
-      <x:c r="K36" s="6" t="n">
-        <x:v>0.221</x:v>
-      </x:c>
-      <x:c r="L36" s="6" t="n">
         <x:v>0.27</x:v>
       </x:c>
+      <x:c r="K36" s="6"/>
+      <x:c r="L36" s="6"/>
       <x:c r="M36" s="6" t="n">
-        <x:v>0.26</x:v>
-      </x:c>
-      <x:c r="N36" s="9" t="n">
-        <x:v>0.247</x:v>
+        <x:v>0.249</x:v>
+      </x:c>
+      <x:c r="N36" s="6" t="n">
+        <x:v>0.275</x:v>
       </x:c>
       <x:c r="O36" s="6" t="n">
-        <x:v>0.249</x:v>
+        <x:v>0.223</x:v>
       </x:c>
       <x:c r="P36" s="6" t="n">
-        <x:v>0.275</x:v>
+        <x:v>0.285</x:v>
       </x:c>
       <x:c r="Q36" s="6" t="n">
-        <x:v>0.223</x:v>
+        <x:v>0.269</x:v>
       </x:c>
       <x:c r="R36" s="6" t="n">
-        <x:v>0.285</x:v>
-      </x:c>
-      <x:c r="S36" s="6" t="n">
-        <x:v>0.269</x:v>
-      </x:c>
-      <x:c r="T36" s="6" t="n">
         <x:v>0.299</x:v>
       </x:c>
+      <x:c r="S36" s="6"/>
+      <x:c r="T36" s="6"/>
       <x:c r="U36" s="6" t="n">
-        <x:v>0.356</x:v>
+        <x:v>0.357</x:v>
       </x:c>
       <x:c r="V36" s="6" t="n">
-        <x:v>0.413</x:v>
-      </x:c>
-      <x:c r="W36" s="6" t="n">
-        <x:v>0.357</x:v>
-      </x:c>
-      <x:c r="X36" s="6" t="n">
         <x:v>0.427</x:v>
       </x:c>
     </x:row>
@@ -2984,67 +2548,61 @@
       <x:c r="C37" s="8" t="n">
         <x:v>0.182</x:v>
       </x:c>
-      <x:c r="D37" s="6" t="n">
+      <x:c r="D37" s="8" t="n">
         <x:v>0.242</x:v>
       </x:c>
       <x:c r="E37" s="6" t="n">
-        <x:v>0.197</x:v>
-      </x:c>
-      <x:c r="F37" s="8" t="n">
-        <x:v>0.223</x:v>
-      </x:c>
-      <x:c r="G37" s="6" t="n">
         <x:v>0.227</x:v>
       </x:c>
-      <x:c r="H37" s="6" t="n">
+      <x:c r="F37" s="6" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="I37" s="9" t="n">
+      <x:c r="G37" s="10" t="n">
         <x:v>0.184</x:v>
       </x:c>
+      <x:c r="H37" s="10" t="n">
+        <x:v>0.247</x:v>
+      </x:c>
+      <x:c r="I37" s="6" t="n">
+        <x:v>0.207</x:v>
+      </x:c>
       <x:c r="J37" s="6" t="n">
-        <x:v>0.247</x:v>
+        <x:v>0.255</x:v>
       </x:c>
       <x:c r="K37" s="6" t="n">
-        <x:v>0.207</x:v>
+        <x:v>0.253</x:v>
       </x:c>
       <x:c r="L37" s="6" t="n">
-        <x:v>0.255</x:v>
+        <x:v>0.272</x:v>
       </x:c>
       <x:c r="M37" s="6" t="n">
-        <x:v>0.238</x:v>
-      </x:c>
-      <x:c r="N37" s="9" t="n">
-        <x:v>0.236</x:v>
+        <x:v>0.233</x:v>
+      </x:c>
+      <x:c r="N37" s="6" t="n">
+        <x:v>0.261</x:v>
       </x:c>
       <x:c r="O37" s="6" t="n">
-        <x:v>0.233</x:v>
+        <x:v>0.216</x:v>
       </x:c>
       <x:c r="P37" s="6" t="n">
-        <x:v>0.261</x:v>
+        <x:v>0.279</x:v>
       </x:c>
       <x:c r="Q37" s="6" t="n">
-        <x:v>0.216</x:v>
+        <x:v>0.254</x:v>
       </x:c>
       <x:c r="R37" s="6" t="n">
-        <x:v>0.279</x:v>
+        <x:v>0.288</x:v>
       </x:c>
       <x:c r="S37" s="6" t="n">
-        <x:v>0.254</x:v>
+        <x:v>0.301</x:v>
       </x:c>
       <x:c r="T37" s="6" t="n">
-        <x:v>0.288</x:v>
+        <x:v>0.319</x:v>
       </x:c>
       <x:c r="U37" s="6" t="n">
-        <x:v>0.329</x:v>
+        <x:v>0.291</x:v>
       </x:c>
       <x:c r="V37" s="6" t="n">
-        <x:v>0.401</x:v>
-      </x:c>
-      <x:c r="W37" s="6" t="n">
-        <x:v>0.291</x:v>
-      </x:c>
-      <x:c r="X37" s="6" t="n">
         <x:v>0.381</x:v>
       </x:c>
     </x:row>
@@ -3061,60 +2619,46 @@
       <x:c r="D38" s="6" t="n">
         <x:v>0.202</x:v>
       </x:c>
-      <x:c r="E38" s="6" t="n">
-        <x:v>0.083</x:v>
-      </x:c>
-      <x:c r="F38" s="6" t="n">
-        <x:v>0.202</x:v>
-      </x:c>
-      <x:c r="G38" s="6"/>
-      <x:c r="H38" s="6"/>
-      <x:c r="I38" s="6" t="n">
+      <x:c r="E38" s="6"/>
+      <x:c r="F38" s="6"/>
+      <x:c r="G38" s="6" t="n">
         <x:v>0.085</x:v>
       </x:c>
-      <x:c r="J38" s="6" t="n">
+      <x:c r="H38" s="6" t="n">
         <x:v>0.204</x:v>
       </x:c>
-      <x:c r="K38" s="9" t="n">
+      <x:c r="I38" s="10" t="n">
         <x:v>0.081</x:v>
       </x:c>
-      <x:c r="L38" s="9" t="n">
+      <x:c r="J38" s="10" t="n">
         <x:v>0.199</x:v>
       </x:c>
+      <x:c r="K38" s="6"/>
+      <x:c r="L38" s="6"/>
       <x:c r="M38" s="6" t="n">
-        <x:v>0.082</x:v>
-      </x:c>
-      <x:c r="N38" s="9" t="n">
-        <x:v>0.199</x:v>
+        <x:v>0.086</x:v>
+      </x:c>
+      <x:c r="N38" s="6" t="n">
+        <x:v>0.206</x:v>
       </x:c>
       <x:c r="O38" s="6" t="n">
-        <x:v>0.086</x:v>
+        <x:v>0.087</x:v>
       </x:c>
       <x:c r="P38" s="6" t="n">
         <x:v>0.206</x:v>
       </x:c>
-      <x:c r="Q38" s="6" t="n">
-        <x:v>0.087</x:v>
-      </x:c>
-      <x:c r="R38" s="6" t="n">
-        <x:v>0.206</x:v>
-      </x:c>
-      <x:c r="S38" s="8" t="n">
+      <x:c r="Q38" s="8" t="n">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="T38" s="8" t="n">
+      <x:c r="R38" s="8" t="n">
         <x:v>0.196</x:v>
       </x:c>
+      <x:c r="S38" s="6"/>
+      <x:c r="T38" s="6"/>
       <x:c r="U38" s="6" t="n">
-        <x:v>0.088</x:v>
+        <x:v>0.131</x:v>
       </x:c>
       <x:c r="V38" s="6" t="n">
-        <x:v>0.218</x:v>
-      </x:c>
-      <x:c r="W38" s="6" t="n">
-        <x:v>0.131</x:v>
-      </x:c>
-      <x:c r="X38" s="6" t="n">
         <x:v>0.284</x:v>
       </x:c>
     </x:row>
@@ -3125,66 +2669,52 @@
       <x:c r="B39" s="4" t="n">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="C39" s="9" t="n">
+      <x:c r="C39" s="10" t="n">
         <x:v>0.176</x:v>
       </x:c>
       <x:c r="D39" s="6" t="n">
         <x:v>0.299</x:v>
       </x:c>
-      <x:c r="E39" s="9" t="n">
-        <x:v>0.176</x:v>
-      </x:c>
-      <x:c r="F39" s="6" t="n">
-        <x:v>0.299</x:v>
-      </x:c>
-      <x:c r="G39" s="6"/>
-      <x:c r="H39" s="6"/>
-      <x:c r="I39" s="6" t="n">
+      <x:c r="E39" s="6"/>
+      <x:c r="F39" s="6"/>
+      <x:c r="G39" s="6" t="n">
         <x:v>0.178</x:v>
       </x:c>
-      <x:c r="J39" s="6" t="n">
+      <x:c r="H39" s="6" t="n">
         <x:v>0.301</x:v>
       </x:c>
-      <x:c r="K39" s="8" t="n">
+      <x:c r="I39" s="8" t="n">
         <x:v>0.171</x:v>
       </x:c>
-      <x:c r="L39" s="9" t="n">
+      <x:c r="J39" s="10" t="n">
         <x:v>0.294</x:v>
       </x:c>
+      <x:c r="K39" s="6"/>
+      <x:c r="L39" s="6"/>
       <x:c r="M39" s="6" t="n">
         <x:v>0.177</x:v>
       </x:c>
       <x:c r="N39" s="6" t="n">
-        <x:v>0.298</x:v>
+        <x:v>0.299</x:v>
       </x:c>
       <x:c r="O39" s="6" t="n">
-        <x:v>0.177</x:v>
+        <x:v>0.193</x:v>
       </x:c>
       <x:c r="P39" s="6" t="n">
-        <x:v>0.299</x:v>
-      </x:c>
-      <x:c r="Q39" s="6" t="n">
-        <x:v>0.193</x:v>
-      </x:c>
-      <x:c r="R39" s="6" t="n">
         <x:v>0.31</x:v>
       </x:c>
-      <x:c r="S39" s="8" t="n">
+      <x:c r="Q39" s="8" t="n">
         <x:v>0.171</x:v>
       </x:c>
-      <x:c r="T39" s="8" t="n">
+      <x:c r="R39" s="8" t="n">
         <x:v>0.293</x:v>
       </x:c>
-      <x:c r="U39" s="9" t="n">
-        <x:v>0.176</x:v>
+      <x:c r="S39" s="6"/>
+      <x:c r="T39" s="6"/>
+      <x:c r="U39" s="6" t="n">
+        <x:v>0.277</x:v>
       </x:c>
       <x:c r="V39" s="6" t="n">
-        <x:v>0.315</x:v>
-      </x:c>
-      <x:c r="W39" s="6" t="n">
-        <x:v>0.277</x:v>
-      </x:c>
-      <x:c r="X39" s="6" t="n">
         <x:v>0.42</x:v>
       </x:c>
     </x:row>
@@ -3201,60 +2731,46 @@
       <x:c r="D40" s="6" t="n">
         <x:v>0.411</x:v>
       </x:c>
-      <x:c r="E40" s="6" t="n">
-        <x:v>0.334</x:v>
-      </x:c>
-      <x:c r="F40" s="6" t="n">
+      <x:c r="E40" s="6"/>
+      <x:c r="F40" s="6"/>
+      <x:c r="G40" s="6" t="n">
+        <x:v>0.339</x:v>
+      </x:c>
+      <x:c r="H40" s="6" t="n">
+        <x:v>0.422</x:v>
+      </x:c>
+      <x:c r="I40" s="10" t="n">
+        <x:v>0.321</x:v>
+      </x:c>
+      <x:c r="J40" s="10" t="n">
+        <x:v>0.409</x:v>
+      </x:c>
+      <x:c r="K40" s="6"/>
+      <x:c r="L40" s="6"/>
+      <x:c r="M40" s="6" t="n">
+        <x:v>0.331</x:v>
+      </x:c>
+      <x:c r="N40" s="6" t="n">
         <x:v>0.417</x:v>
       </x:c>
-      <x:c r="G40" s="6"/>
-      <x:c r="H40" s="6"/>
-      <x:c r="I40" s="6" t="n">
-        <x:v>0.339</x:v>
-      </x:c>
-      <x:c r="J40" s="6" t="n">
-        <x:v>0.422</x:v>
-      </x:c>
-      <x:c r="K40" s="6" t="n">
-        <x:v>0.321</x:v>
-      </x:c>
-      <x:c r="L40" s="9" t="n">
-        <x:v>0.409</x:v>
-      </x:c>
-      <x:c r="M40" s="6" t="n">
-        <x:v>0.349</x:v>
-      </x:c>
-      <x:c r="N40" s="6" t="n">
+      <x:c r="O40" s="6" t="n">
+        <x:v>0.345</x:v>
+      </x:c>
+      <x:c r="P40" s="6" t="n">
         <x:v>0.425</x:v>
       </x:c>
-      <x:c r="O40" s="6" t="n">
-        <x:v>0.331</x:v>
-      </x:c>
-      <x:c r="P40" s="6" t="n">
-        <x:v>0.417</x:v>
-      </x:c>
-      <x:c r="Q40" s="6" t="n">
-        <x:v>0.345</x:v>
-      </x:c>
-      <x:c r="R40" s="6" t="n">
-        <x:v>0.425</x:v>
-      </x:c>
-      <x:c r="S40" s="9" t="n">
+      <x:c r="Q40" s="8" t="n">
         <x:v>0.317</x:v>
       </x:c>
-      <x:c r="T40" s="8" t="n">
+      <x:c r="R40" s="8" t="n">
         <x:v>0.406</x:v>
       </x:c>
-      <x:c r="U40" s="8" t="n">
-        <x:v>0.313</x:v>
+      <x:c r="S40" s="6"/>
+      <x:c r="T40" s="6"/>
+      <x:c r="U40" s="6" t="n">
+        <x:v>0.426</x:v>
       </x:c>
       <x:c r="V40" s="6" t="n">
-        <x:v>0.427</x:v>
-      </x:c>
-      <x:c r="W40" s="6" t="n">
-        <x:v>0.426</x:v>
-      </x:c>
-      <x:c r="X40" s="6" t="n">
         <x:v>0.511</x:v>
       </x:c>
     </x:row>
@@ -3271,60 +2787,46 @@
       <x:c r="D41" s="8" t="n">
         <x:v>0.672</x:v>
       </x:c>
-      <x:c r="E41" s="9" t="n">
-        <x:v>0.827</x:v>
-      </x:c>
-      <x:c r="F41" s="9" t="n">
+      <x:c r="E41" s="6"/>
+      <x:c r="F41" s="6"/>
+      <x:c r="G41" s="6" t="n">
+        <x:v>0.873</x:v>
+      </x:c>
+      <x:c r="H41" s="6" t="n">
+        <x:v>0.705</x:v>
+      </x:c>
+      <x:c r="I41" s="10" t="n">
+        <x:v>0.837</x:v>
+      </x:c>
+      <x:c r="J41" s="10" t="n">
         <x:v>0.688</x:v>
       </x:c>
-      <x:c r="G41" s="6"/>
-      <x:c r="H41" s="6"/>
-      <x:c r="I41" s="6" t="n">
-        <x:v>0.873</x:v>
-      </x:c>
-      <x:c r="J41" s="6" t="n">
-        <x:v>0.705</x:v>
-      </x:c>
-      <x:c r="K41" s="6" t="n">
-        <x:v>0.837</x:v>
-      </x:c>
-      <x:c r="L41" s="9" t="n">
-        <x:v>0.688</x:v>
-      </x:c>
+      <x:c r="K41" s="6"/>
+      <x:c r="L41" s="6"/>
       <x:c r="M41" s="6" t="n">
-        <x:v>0.891</x:v>
+        <x:v>0.847</x:v>
       </x:c>
       <x:c r="N41" s="6" t="n">
-        <x:v>0.711</x:v>
+        <x:v>0.691</x:v>
       </x:c>
       <x:c r="O41" s="6" t="n">
-        <x:v>0.847</x:v>
+        <x:v>1.008</x:v>
       </x:c>
       <x:c r="P41" s="6" t="n">
-        <x:v>0.691</x:v>
+        <x:v>0.747</x:v>
       </x:c>
       <x:c r="Q41" s="6" t="n">
-        <x:v>1.008</x:v>
+        <x:v>0.887</x:v>
       </x:c>
       <x:c r="R41" s="6" t="n">
-        <x:v>0.747</x:v>
-      </x:c>
-      <x:c r="S41" s="6" t="n">
-        <x:v>0.887</x:v>
-      </x:c>
-      <x:c r="T41" s="6" t="n">
         <x:v>0.703</x:v>
       </x:c>
+      <x:c r="S41" s="6"/>
+      <x:c r="T41" s="6"/>
       <x:c r="U41" s="6" t="n">
-        <x:v>0.839</x:v>
+        <x:v>1.162</x:v>
       </x:c>
       <x:c r="V41" s="6" t="n">
-        <x:v>0.695</x:v>
-      </x:c>
-      <x:c r="W41" s="6" t="n">
-        <x:v>1.162</x:v>
-      </x:c>
-      <x:c r="X41" s="6" t="n">
         <x:v>0.832</x:v>
       </x:c>
     </x:row>
@@ -3335,66 +2837,60 @@
       <x:c r="B42" s="4" t="str">
         <x:v>AVG</x:v>
       </x:c>
-      <x:c r="C42" s="8" t="n">
+      <x:c r="C42" s="10" t="n">
         <x:v>0.344</x:v>
       </x:c>
-      <x:c r="D42" s="8" t="n">
+      <x:c r="D42" s="10" t="n">
         <x:v>0.396</x:v>
       </x:c>
-      <x:c r="E42" s="6" t="n">
-        <x:v>0.355</x:v>
-      </x:c>
-      <x:c r="F42" s="6" t="n">
-        <x:v>0.401</x:v>
-      </x:c>
-      <x:c r="G42" s="6"/>
-      <x:c r="H42" s="6"/>
+      <x:c r="E42" s="6"/>
+      <x:c r="F42" s="6"/>
+      <x:c r="G42" s="6" t="n">
+        <x:v>0.368</x:v>
+      </x:c>
+      <x:c r="H42" s="6" t="n">
+        <x:v>0.408</x:v>
+      </x:c>
       <x:c r="I42" s="6" t="n">
-        <x:v>0.368</x:v>
+        <x:v>0.352</x:v>
       </x:c>
       <x:c r="J42" s="6" t="n">
+        <x:v>0.397</x:v>
+      </x:c>
+      <x:c r="K42" s="8" t="n">
+        <x:v>0.342</x:v>
+      </x:c>
+      <x:c r="L42" s="8" t="n">
+        <x:v>0.392</x:v>
+      </x:c>
+      <x:c r="M42" s="6" t="n">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="N42" s="6" t="n">
+        <x:v>0.403</x:v>
+      </x:c>
+      <x:c r="O42" s="6" t="n">
         <x:v>0.408</x:v>
       </x:c>
-      <x:c r="K42" s="9" t="n">
-        <x:v>0.352</x:v>
-      </x:c>
-      <x:c r="L42" s="9" t="n">
-        <x:v>0.397</x:v>
-      </x:c>
-      <x:c r="M42" s="6" t="n">
-        <x:v>0.374</x:v>
-      </x:c>
-      <x:c r="N42" s="6" t="n">
-        <x:v>0.408</x:v>
-      </x:c>
-      <x:c r="O42" s="6" t="n">
-        <x:v>0.36</x:v>
-      </x:c>
       <x:c r="P42" s="6" t="n">
-        <x:v>0.403</x:v>
+        <x:v>0.422</x:v>
       </x:c>
       <x:c r="Q42" s="6" t="n">
-        <x:v>0.408</x:v>
+        <x:v>0.363</x:v>
       </x:c>
       <x:c r="R42" s="6" t="n">
-        <x:v>0.422</x:v>
+        <x:v>0.399</x:v>
       </x:c>
       <x:c r="S42" s="6" t="n">
-        <x:v>0.363</x:v>
+        <x:v>0.416</x:v>
       </x:c>
       <x:c r="T42" s="6" t="n">
-        <x:v>0.399</x:v>
+        <x:v>0.443</x:v>
       </x:c>
       <x:c r="U42" s="6" t="n">
-        <x:v>0.354</x:v>
+        <x:v>0.499</x:v>
       </x:c>
       <x:c r="V42" s="6" t="n">
-        <x:v>0.413</x:v>
-      </x:c>
-      <x:c r="W42" s="6" t="n">
-        <x:v>0.499</x:v>
-      </x:c>
-      <x:c r="X42" s="6" t="n">
         <x:v>0.511</x:v>
       </x:c>
     </x:row>
@@ -3408,67 +2904,53 @@
       <x:c r="C43" s="6" t="n">
         <x:v>0.41</x:v>
       </x:c>
-      <x:c r="D43" s="9" t="n">
+      <x:c r="D43" s="8" t="n">
         <x:v>0.255</x:v>
       </x:c>
-      <x:c r="E43" s="6" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="F43" s="8" t="n">
-        <x:v>0.237</x:v>
-      </x:c>
-      <x:c r="G43" s="8" t="n">
+      <x:c r="E43" s="8" t="n">
         <x:v>0.386</x:v>
       </x:c>
+      <x:c r="F43" s="10" t="n">
+        <x:v>0.258</x:v>
+      </x:c>
+      <x:c r="G43" s="6" t="n">
+        <x:v>0.41</x:v>
+      </x:c>
       <x:c r="H43" s="6" t="n">
-        <x:v>0.258</x:v>
+        <x:v>0.274</x:v>
       </x:c>
       <x:c r="I43" s="6" t="n">
-        <x:v>0.41</x:v>
+        <x:v>0.448</x:v>
       </x:c>
       <x:c r="J43" s="6" t="n">
-        <x:v>0.274</x:v>
-      </x:c>
-      <x:c r="K43" s="6" t="n">
-        <x:v>0.448</x:v>
-      </x:c>
-      <x:c r="L43" s="6" t="n">
         <x:v>0.309</x:v>
       </x:c>
-      <x:c r="M43" s="6" t="n">
-        <x:v>0.471</x:v>
+      <x:c r="K43" s="6"/>
+      <x:c r="L43" s="6"/>
+      <x:c r="M43" s="10" t="n">
+        <x:v>0.395</x:v>
       </x:c>
       <x:c r="N43" s="6" t="n">
-        <x:v>0.275</x:v>
-      </x:c>
-      <x:c r="O43" s="9" t="n">
-        <x:v>0.395</x:v>
+        <x:v>0.268</x:v>
+      </x:c>
+      <x:c r="O43" s="6" t="n">
+        <x:v>0.469</x:v>
       </x:c>
       <x:c r="P43" s="6" t="n">
-        <x:v>0.268</x:v>
+        <x:v>0.287</x:v>
       </x:c>
       <x:c r="Q43" s="6" t="n">
-        <x:v>0.469</x:v>
+        <x:v>0.462</x:v>
       </x:c>
       <x:c r="R43" s="6" t="n">
-        <x:v>0.287</x:v>
-      </x:c>
-      <x:c r="S43" s="6" t="n">
-        <x:v>0.462</x:v>
-      </x:c>
-      <x:c r="T43" s="6" t="n">
         <x:v>0.295</x:v>
       </x:c>
+      <x:c r="S43" s="6"/>
+      <x:c r="T43" s="6"/>
       <x:c r="U43" s="6" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.587</x:v>
       </x:c>
       <x:c r="V43" s="6" t="n">
-        <x:v>0.396</x:v>
-      </x:c>
-      <x:c r="W43" s="6" t="n">
-        <x:v>0.587</x:v>
-      </x:c>
-      <x:c r="X43" s="6" t="n">
         <x:v>0.366</x:v>
       </x:c>
     </x:row>
@@ -3482,67 +2964,53 @@
       <x:c r="C44" s="6" t="n">
         <x:v>0.424</x:v>
       </x:c>
-      <x:c r="D44" s="6" t="n">
+      <x:c r="D44" s="10" t="n">
         <x:v>0.265</x:v>
       </x:c>
-      <x:c r="E44" s="6" t="n">
-        <x:v>0.418</x:v>
+      <x:c r="E44" s="8" t="n">
+        <x:v>0.398</x:v>
       </x:c>
       <x:c r="F44" s="8" t="n">
-        <x:v>0.249</x:v>
-      </x:c>
-      <x:c r="G44" s="8" t="n">
-        <x:v>0.398</x:v>
-      </x:c>
-      <x:c r="H44" s="9" t="n">
         <x:v>0.263</x:v>
       </x:c>
+      <x:c r="G44" s="6" t="n">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="H44" s="6" t="n">
+        <x:v>0.28</x:v>
+      </x:c>
       <x:c r="I44" s="6" t="n">
-        <x:v>0.43</x:v>
+        <x:v>0.455</x:v>
       </x:c>
       <x:c r="J44" s="6" t="n">
-        <x:v>0.28</x:v>
-      </x:c>
-      <x:c r="K44" s="6" t="n">
-        <x:v>0.455</x:v>
-      </x:c>
-      <x:c r="L44" s="6" t="n">
         <x:v>0.307</x:v>
       </x:c>
-      <x:c r="M44" s="6" t="n">
-        <x:v>0.478</x:v>
+      <x:c r="K44" s="6"/>
+      <x:c r="L44" s="6"/>
+      <x:c r="M44" s="10" t="n">
+        <x:v>0.417</x:v>
       </x:c>
       <x:c r="N44" s="6" t="n">
-        <x:v>0.272</x:v>
-      </x:c>
-      <x:c r="O44" s="9" t="n">
-        <x:v>0.417</x:v>
+        <x:v>0.276</x:v>
+      </x:c>
+      <x:c r="O44" s="6" t="n">
+        <x:v>0.476</x:v>
       </x:c>
       <x:c r="P44" s="6" t="n">
-        <x:v>0.276</x:v>
+        <x:v>0.296</x:v>
       </x:c>
       <x:c r="Q44" s="6" t="n">
-        <x:v>0.476</x:v>
+        <x:v>0.466</x:v>
       </x:c>
       <x:c r="R44" s="6" t="n">
         <x:v>0.296</x:v>
       </x:c>
-      <x:c r="S44" s="6" t="n">
-        <x:v>0.466</x:v>
-      </x:c>
-      <x:c r="T44" s="6" t="n">
-        <x:v>0.296</x:v>
-      </x:c>
+      <x:c r="S44" s="6"/>
+      <x:c r="T44" s="6"/>
       <x:c r="U44" s="6" t="n">
-        <x:v>0.598</x:v>
+        <x:v>0.604</x:v>
       </x:c>
       <x:c r="V44" s="6" t="n">
-        <x:v>0.37</x:v>
-      </x:c>
-      <x:c r="W44" s="6" t="n">
-        <x:v>0.604</x:v>
-      </x:c>
-      <x:c r="X44" s="6" t="n">
         <x:v>0.373</x:v>
       </x:c>
     </x:row>
@@ -3556,67 +3024,53 @@
       <x:c r="C45" s="6" t="n">
         <x:v>0.441</x:v>
       </x:c>
-      <x:c r="D45" s="6" t="n">
+      <x:c r="D45" s="10" t="n">
         <x:v>0.272</x:v>
       </x:c>
-      <x:c r="E45" s="6" t="n">
-        <x:v>0.438</x:v>
+      <x:c r="E45" s="8" t="n">
+        <x:v>0.409</x:v>
       </x:c>
       <x:c r="F45" s="8" t="n">
-        <x:v>0.256</x:v>
-      </x:c>
-      <x:c r="G45" s="8" t="n">
-        <x:v>0.409</x:v>
-      </x:c>
-      <x:c r="H45" s="9" t="n">
         <x:v>0.27</x:v>
       </x:c>
+      <x:c r="G45" s="6" t="n">
+        <x:v>0.449</x:v>
+      </x:c>
+      <x:c r="H45" s="6" t="n">
+        <x:v>0.29</x:v>
+      </x:c>
       <x:c r="I45" s="6" t="n">
-        <x:v>0.449</x:v>
+        <x:v>0.472</x:v>
       </x:c>
       <x:c r="J45" s="6" t="n">
-        <x:v>0.29</x:v>
-      </x:c>
-      <x:c r="K45" s="6" t="n">
-        <x:v>0.472</x:v>
-      </x:c>
-      <x:c r="L45" s="6" t="n">
         <x:v>0.313</x:v>
       </x:c>
-      <x:c r="M45" s="6" t="n">
-        <x:v>0.501</x:v>
+      <x:c r="K45" s="6"/>
+      <x:c r="L45" s="6"/>
+      <x:c r="M45" s="10" t="n">
+        <x:v>0.433</x:v>
       </x:c>
       <x:c r="N45" s="6" t="n">
-        <x:v>0.276</x:v>
-      </x:c>
-      <x:c r="O45" s="9" t="n">
-        <x:v>0.433</x:v>
+        <x:v>0.283</x:v>
+      </x:c>
+      <x:c r="O45" s="6" t="n">
+        <x:v>0.488</x:v>
       </x:c>
       <x:c r="P45" s="6" t="n">
-        <x:v>0.283</x:v>
+        <x:v>0.299</x:v>
       </x:c>
       <x:c r="Q45" s="6" t="n">
-        <x:v>0.488</x:v>
+        <x:v>0.482</x:v>
       </x:c>
       <x:c r="R45" s="6" t="n">
-        <x:v>0.299</x:v>
-      </x:c>
-      <x:c r="S45" s="6" t="n">
-        <x:v>0.482</x:v>
-      </x:c>
-      <x:c r="T45" s="6" t="n">
         <x:v>0.304</x:v>
       </x:c>
+      <x:c r="S45" s="6"/>
+      <x:c r="T45" s="6"/>
       <x:c r="U45" s="6" t="n">
-        <x:v>0.605</x:v>
+        <x:v>0.621</x:v>
       </x:c>
       <x:c r="V45" s="6" t="n">
-        <x:v>0.373</x:v>
-      </x:c>
-      <x:c r="W45" s="6" t="n">
-        <x:v>0.621</x:v>
-      </x:c>
-      <x:c r="X45" s="6" t="n">
         <x:v>0.383</x:v>
       </x:c>
     </x:row>
@@ -3630,67 +3084,53 @@
       <x:c r="C46" s="6" t="n">
         <x:v>0.476</x:v>
       </x:c>
-      <x:c r="D46" s="6" t="n">
+      <x:c r="D46" s="10" t="n">
         <x:v>0.29</x:v>
       </x:c>
-      <x:c r="E46" s="6" t="n">
-        <x:v>0.47</x:v>
+      <x:c r="E46" s="8" t="n">
+        <x:v>0.431</x:v>
       </x:c>
       <x:c r="F46" s="8" t="n">
-        <x:v>0.275</x:v>
-      </x:c>
-      <x:c r="G46" s="8" t="n">
-        <x:v>0.431</x:v>
-      </x:c>
-      <x:c r="H46" s="9" t="n">
         <x:v>0.287</x:v>
       </x:c>
+      <x:c r="G46" s="6" t="n">
+        <x:v>0.486</x:v>
+      </x:c>
+      <x:c r="H46" s="6" t="n">
+        <x:v>0.309</x:v>
+      </x:c>
       <x:c r="I46" s="6" t="n">
-        <x:v>0.486</x:v>
+        <x:v>0.508</x:v>
       </x:c>
       <x:c r="J46" s="6" t="n">
-        <x:v>0.309</x:v>
-      </x:c>
-      <x:c r="K46" s="6" t="n">
-        <x:v>0.508</x:v>
-      </x:c>
-      <x:c r="L46" s="6" t="n">
         <x:v>0.332</x:v>
       </x:c>
-      <x:c r="M46" s="6" t="n">
-        <x:v>0.547</x:v>
+      <x:c r="K46" s="6"/>
+      <x:c r="L46" s="6"/>
+      <x:c r="M46" s="10" t="n">
+        <x:v>0.467</x:v>
       </x:c>
       <x:c r="N46" s="6" t="n">
-        <x:v>0.291</x:v>
-      </x:c>
-      <x:c r="O46" s="9" t="n">
-        <x:v>0.467</x:v>
+        <x:v>0.302</x:v>
+      </x:c>
+      <x:c r="O46" s="6" t="n">
+        <x:v>0.522</x:v>
       </x:c>
       <x:c r="P46" s="6" t="n">
-        <x:v>0.302</x:v>
+        <x:v>0.316</x:v>
       </x:c>
       <x:c r="Q46" s="6" t="n">
-        <x:v>0.522</x:v>
+        <x:v>0.514</x:v>
       </x:c>
       <x:c r="R46" s="6" t="n">
-        <x:v>0.316</x:v>
-      </x:c>
-      <x:c r="S46" s="6" t="n">
-        <x:v>0.514</x:v>
-      </x:c>
-      <x:c r="T46" s="6" t="n">
         <x:v>0.322</x:v>
       </x:c>
+      <x:c r="S46" s="6"/>
+      <x:c r="T46" s="6"/>
       <x:c r="U46" s="6" t="n">
-        <x:v>0.645</x:v>
+        <x:v>0.626</x:v>
       </x:c>
       <x:c r="V46" s="6" t="n">
-        <x:v>0.394</x:v>
-      </x:c>
-      <x:c r="W46" s="6" t="n">
-        <x:v>0.626</x:v>
-      </x:c>
-      <x:c r="X46" s="6" t="n">
         <x:v>0.382</x:v>
       </x:c>
     </x:row>
@@ -3704,67 +3144,61 @@
       <x:c r="C47" s="6" t="n">
         <x:v>0.438</x:v>
       </x:c>
-      <x:c r="D47" s="6" t="n">
+      <x:c r="D47" s="10" t="n">
         <x:v>0.27</x:v>
       </x:c>
-      <x:c r="E47" s="6" t="n">
-        <x:v>0.431</x:v>
+      <x:c r="E47" s="8" t="n">
+        <x:v>0.406</x:v>
       </x:c>
       <x:c r="F47" s="8" t="n">
-        <x:v>0.254</x:v>
-      </x:c>
-      <x:c r="G47" s="8" t="n">
-        <x:v>0.406</x:v>
-      </x:c>
-      <x:c r="H47" s="9" t="n">
         <x:v>0.269</x:v>
       </x:c>
+      <x:c r="G47" s="6" t="n">
+        <x:v>0.443</x:v>
+      </x:c>
+      <x:c r="H47" s="6" t="n">
+        <x:v>0.288</x:v>
+      </x:c>
       <x:c r="I47" s="6" t="n">
-        <x:v>0.443</x:v>
+        <x:v>0.47</x:v>
       </x:c>
       <x:c r="J47" s="6" t="n">
-        <x:v>0.288</x:v>
+        <x:v>0.315</x:v>
       </x:c>
       <x:c r="K47" s="6" t="n">
-        <x:v>0.47</x:v>
+        <x:v>0.472</x:v>
       </x:c>
       <x:c r="L47" s="6" t="n">
-        <x:v>0.315</x:v>
-      </x:c>
-      <x:c r="M47" s="6" t="n">
-        <x:v>0.499</x:v>
+        <x:v>0.303</x:v>
+      </x:c>
+      <x:c r="M47" s="10" t="n">
+        <x:v>0.428</x:v>
       </x:c>
       <x:c r="N47" s="6" t="n">
-        <x:v>0.278</x:v>
-      </x:c>
-      <x:c r="O47" s="9" t="n">
-        <x:v>0.428</x:v>
+        <x:v>0.282</x:v>
+      </x:c>
+      <x:c r="O47" s="6" t="n">
+        <x:v>0.488</x:v>
       </x:c>
       <x:c r="P47" s="6" t="n">
-        <x:v>0.282</x:v>
+        <x:v>0.299</x:v>
       </x:c>
       <x:c r="Q47" s="6" t="n">
-        <x:v>0.488</x:v>
+        <x:v>0.481</x:v>
       </x:c>
       <x:c r="R47" s="6" t="n">
-        <x:v>0.299</x:v>
+        <x:v>0.304</x:v>
       </x:c>
       <x:c r="S47" s="6" t="n">
-        <x:v>0.481</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="T47" s="6" t="n">
-        <x:v>0.304</x:v>
+        <x:v>0.336</x:v>
       </x:c>
       <x:c r="U47" s="6" t="n">
-        <x:v>0.624</x:v>
+        <x:v>0.609</x:v>
       </x:c>
       <x:c r="V47" s="6" t="n">
-        <x:v>0.383</x:v>
-      </x:c>
-      <x:c r="W47" s="6" t="n">
-        <x:v>0.609</x:v>
-      </x:c>
-      <x:c r="X47" s="6" t="n">
         <x:v>0.376</x:v>
       </x:c>
     </x:row>
@@ -3774,15 +3208,15 @@
       </x:c>
       <x:c r="B48" s="7"/>
       <x:c r="C48" s="7" t="n">
-        <x:v>25</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D48" s="7"/>
       <x:c r="E48" s="7" t="n">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F48" s="7"/>
       <x:c r="G48" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H48" s="7"/>
       <x:c r="I48" s="7" t="n">
@@ -3790,11 +3224,11 @@
       </x:c>
       <x:c r="J48" s="7"/>
       <x:c r="K48" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L48" s="7"/>
       <x:c r="M48" s="7" t="n">
-        <x:v>26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N48" s="7"/>
       <x:c r="O48" s="7" t="n">
@@ -3802,21 +3236,22 @@
       </x:c>
       <x:c r="P48" s="7"/>
       <x:c r="Q48" s="7" t="n">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="R48" s="7"/>
       <x:c r="S48" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="T48" s="7"/>
       <x:c r="U48" s="7" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="V48" s="7"/>
-      <x:c r="W48" s="7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X48" s="7"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="9" t="str">
+        <x:v>空白=来源未报告：FACTS/TimesNet 仅有论文报告的数据集平均，无本地逐预测长度结果；DeepBooTS 缺 Exchange。 E-Armor 与其余基线为本地结果，AVG 由 96/192/336/720 全精度值取均值后截断。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3832,7 +3267,6 @@
     <x:mergeCell ref="Q1:R1"/>
     <x:mergeCell ref="S1:T1"/>
     <x:mergeCell ref="U1:V1"/>
-    <x:mergeCell ref="W1:X1"/>
     <x:mergeCell ref="A3:A7"/>
     <x:mergeCell ref="A8:A12"/>
     <x:mergeCell ref="A13:A17"/>
@@ -3853,7 +3287,1276 @@
     <x:mergeCell ref="Q48:R48"/>
     <x:mergeCell ref="S48:T48"/>
     <x:mergeCell ref="U48:V48"/>
-    <x:mergeCell ref="W48:X48"/>
+    <x:mergeCell ref="A50:V50"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="9" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Dataset</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="str">
+        <x:v>Prediction Length</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="str">
+        <x:v>EMAformer</x:v>
+      </x:c>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5" t="str">
+        <x:v>xPatch</x:v>
+      </x:c>
+      <x:c r="F1" s="5"/>
+      <x:c r="G1" s="5" t="str">
+        <x:v>DLinear</x:v>
+      </x:c>
+      <x:c r="H1" s="5"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="5"/>
+      <x:c r="B2" s="5"/>
+      <x:c r="C2" s="5" t="str">
+        <x:v>MSE</x:v>
+      </x:c>
+      <x:c r="D2" s="5" t="str">
+        <x:v>MAE</x:v>
+      </x:c>
+      <x:c r="E2" s="5" t="str">
+        <x:v>MSE</x:v>
+      </x:c>
+      <x:c r="F2" s="5" t="str">
+        <x:v>MAE</x:v>
+      </x:c>
+      <x:c r="G2" s="5" t="str">
+        <x:v>MSE</x:v>
+      </x:c>
+      <x:c r="H2" s="5" t="str">
+        <x:v>MAE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="20" customHeight="1">
+      <x:c r="A3" s="5" t="str">
+        <x:v>ETTh1</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C3" s="8" t="n">
+        <x:v>0.374</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="n">
+        <x:v>0.389</x:v>
+      </x:c>
+      <x:c r="E3" s="10" t="n">
+        <x:v>0.376</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="n">
+        <x:v>0.386</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="n">
+        <x:v>0.386</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="20" customHeight="1">
+      <x:c r="A4" s="5" t="str">
+        <x:v>ETTh1</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="n">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="n">
+        <x:v>0.418</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="n">
+        <x:v>0.417</x:v>
+      </x:c>
+      <x:c r="F4" s="8" t="n">
+        <x:v>0.407</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="n">
+        <x:v>0.437</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="n">
+        <x:v>0.432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="20" customHeight="1">
+      <x:c r="A5" s="5" t="str">
+        <x:v>ETTh1</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="n">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="n">
+        <x:v>0.468</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="n">
+        <x:v>0.438</x:v>
+      </x:c>
+      <x:c r="E5" s="8" t="n">
+        <x:v>0.449</x:v>
+      </x:c>
+      <x:c r="F5" s="8" t="n">
+        <x:v>0.425</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="n">
+        <x:v>0.481</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="n">
+        <x:v>0.459</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="20" customHeight="1">
+      <x:c r="A6" s="5" t="str">
+        <x:v>ETTh1</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="n">
+        <x:v>0.455</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="E6" s="10" t="n">
+        <x:v>0.47</x:v>
+      </x:c>
+      <x:c r="F6" s="10" t="n">
+        <x:v>0.456</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="n">
+        <x:v>0.519</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="n">
+        <x:v>0.516</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="20" customHeight="1">
+      <x:c r="A7" s="5" t="str">
+        <x:v>ETTh1</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="str">
+        <x:v>AVG</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="n">
+        <x:v>0.431</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="n">
+        <x:v>0.423</x:v>
+      </x:c>
+      <x:c r="E7" s="8" t="n">
+        <x:v>0.428</x:v>
+      </x:c>
+      <x:c r="F7" s="8" t="n">
+        <x:v>0.418</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="n">
+        <x:v>0.455</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="n">
+        <x:v>0.451</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="20" customHeight="1">
+      <x:c r="A8" s="5" t="str">
+        <x:v>ETTm1</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="n">
+        <x:v>0.303</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="n">
+        <x:v>0.336</x:v>
+      </x:c>
+      <x:c r="E8" s="10" t="n">
+        <x:v>0.311</x:v>
+      </x:c>
+      <x:c r="F8" s="10" t="n">
+        <x:v>0.346</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="n">
+        <x:v>0.345</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="n">
+        <x:v>0.372</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="20" customHeight="1">
+      <x:c r="A9" s="5" t="str">
+        <x:v>ETTm1</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="n">
+        <x:v>0.359</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="n">
+        <x:v>0.364</x:v>
+      </x:c>
+      <x:c r="E9" s="8" t="n">
+        <x:v>0.348</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="n">
+        <x:v>0.368</x:v>
+      </x:c>
+      <x:c r="G9" s="6" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="H9" s="6" t="n">
+        <x:v>0.389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="20" customHeight="1">
+      <x:c r="A10" s="5" t="str">
+        <x:v>ETTm1</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="n">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="n">
+        <x:v>0.393</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="n">
+        <x:v>0.387</x:v>
+      </x:c>
+      <x:c r="E10" s="8" t="n">
+        <x:v>0.388</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="n">
+        <x:v>0.391</x:v>
+      </x:c>
+      <x:c r="G10" s="6" t="n">
+        <x:v>0.413</x:v>
+      </x:c>
+      <x:c r="H10" s="6" t="n">
+        <x:v>0.413</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="20" customHeight="1">
+      <x:c r="A11" s="5" t="str">
+        <x:v>ETTm1</x:v>
+      </x:c>
+      <x:c r="B11" s="4" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="n">
+        <x:v>0.467</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="n">
+        <x:v>0.431</x:v>
+      </x:c>
+      <x:c r="E11" s="8" t="n">
+        <x:v>0.461</x:v>
+      </x:c>
+      <x:c r="F11" s="8" t="n">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="G11" s="6" t="n">
+        <x:v>0.474</x:v>
+      </x:c>
+      <x:c r="H11" s="6" t="n">
+        <x:v>0.453</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="20" customHeight="1">
+      <x:c r="A12" s="5" t="str">
+        <x:v>ETTm1</x:v>
+      </x:c>
+      <x:c r="B12" s="4" t="str">
+        <x:v>AVG</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="D12" s="8" t="n">
+        <x:v>0.379</x:v>
+      </x:c>
+      <x:c r="E12" s="8" t="n">
+        <x:v>0.377</x:v>
+      </x:c>
+      <x:c r="F12" s="10" t="n">
+        <x:v>0.383</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="n">
+        <x:v>0.403</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="n">
+        <x:v>0.406</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="20" customHeight="1">
+      <x:c r="A13" s="5" t="str">
+        <x:v>ETTh2</x:v>
+      </x:c>
+      <x:c r="B13" s="4" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="n">
+        <x:v>0.289</x:v>
+      </x:c>
+      <x:c r="D13" s="10" t="n">
+        <x:v>0.334</x:v>
+      </x:c>
+      <x:c r="E13" s="8" t="n">
+        <x:v>0.233</x:v>
+      </x:c>
+      <x:c r="F13" s="8" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="n">
+        <x:v>0.333</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="n">
+        <x:v>0.387</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="20" customHeight="1">
+      <x:c r="A14" s="5" t="str">
+        <x:v>ETTh2</x:v>
+      </x:c>
+      <x:c r="B14" s="4" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="n">
+        <x:v>0.366</x:v>
+      </x:c>
+      <x:c r="D14" s="10" t="n">
+        <x:v>0.385</x:v>
+      </x:c>
+      <x:c r="E14" s="8" t="n">
+        <x:v>0.291</x:v>
+      </x:c>
+      <x:c r="F14" s="8" t="n">
+        <x:v>0.338</x:v>
+      </x:c>
+      <x:c r="G14" s="6" t="n">
+        <x:v>0.477</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="n">
+        <x:v>0.476</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="20" customHeight="1">
+      <x:c r="A15" s="5" t="str">
+        <x:v>ETTh2</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="n">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="n">
+        <x:v>0.413</x:v>
+      </x:c>
+      <x:c r="D15" s="10" t="n">
+        <x:v>0.421</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="n">
+        <x:v>0.344</x:v>
+      </x:c>
+      <x:c r="F15" s="8" t="n">
+        <x:v>0.377</x:v>
+      </x:c>
+      <x:c r="G15" s="6" t="n">
+        <x:v>0.594</x:v>
+      </x:c>
+      <x:c r="H15" s="6" t="n">
+        <x:v>0.541</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="20" customHeight="1">
+      <x:c r="A16" s="5" t="str">
+        <x:v>ETTh2</x:v>
+      </x:c>
+      <x:c r="B16" s="4" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="n">
+        <x:v>0.424</x:v>
+      </x:c>
+      <x:c r="D16" s="10" t="n">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="E16" s="8" t="n">
+        <x:v>0.407</x:v>
+      </x:c>
+      <x:c r="F16" s="8" t="n">
+        <x:v>0.427</x:v>
+      </x:c>
+      <x:c r="G16" s="6" t="n">
+        <x:v>0.831</x:v>
+      </x:c>
+      <x:c r="H16" s="6" t="n">
+        <x:v>0.657</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="20" customHeight="1">
+      <x:c r="A17" s="5" t="str">
+        <x:v>ETTh2</x:v>
+      </x:c>
+      <x:c r="B17" s="4" t="str">
+        <x:v>AVG</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="n">
+        <x:v>0.373</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="n">
+        <x:v>0.394</x:v>
+      </x:c>
+      <x:c r="E17" s="8" t="n">
+        <x:v>0.318</x:v>
+      </x:c>
+      <x:c r="F17" s="8" t="n">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="G17" s="6" t="n">
+        <x:v>0.558</x:v>
+      </x:c>
+      <x:c r="H17" s="6" t="n">
+        <x:v>0.515</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="20" customHeight="1">
+      <x:c r="A18" s="5" t="str">
+        <x:v>ETTm2</x:v>
+      </x:c>
+      <x:c r="B18" s="4" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="n">
+        <x:v>0.167</x:v>
+      </x:c>
+      <x:c r="D18" s="8" t="n">
+        <x:v>0.245</x:v>
+      </x:c>
+      <x:c r="E18" s="8" t="n">
+        <x:v>0.164</x:v>
+      </x:c>
+      <x:c r="F18" s="10" t="n">
+        <x:v>0.248</x:v>
+      </x:c>
+      <x:c r="G18" s="6" t="n">
+        <x:v>0.193</x:v>
+      </x:c>
+      <x:c r="H18" s="6" t="n">
+        <x:v>0.292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="20" customHeight="1">
+      <x:c r="A19" s="5" t="str">
+        <x:v>ETTm2</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="n">
+        <x:v>0.233</x:v>
+      </x:c>
+      <x:c r="D19" s="8" t="n">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="E19" s="8" t="n">
+        <x:v>0.23</x:v>
+      </x:c>
+      <x:c r="F19" s="10" t="n">
+        <x:v>0.291</x:v>
+      </x:c>
+      <x:c r="G19" s="6" t="n">
+        <x:v>0.284</x:v>
+      </x:c>
+      <x:c r="H19" s="6" t="n">
+        <x:v>0.362</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="20" customHeight="1">
+      <x:c r="A20" s="5" t="str">
+        <x:v>ETTm2</x:v>
+      </x:c>
+      <x:c r="B20" s="4" t="n">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="n">
+        <x:v>0.293</x:v>
+      </x:c>
+      <x:c r="D20" s="8" t="n">
+        <x:v>0.328</x:v>
+      </x:c>
+      <x:c r="E20" s="8" t="n">
+        <x:v>0.292</x:v>
+      </x:c>
+      <x:c r="F20" s="10" t="n">
+        <x:v>0.331</x:v>
+      </x:c>
+      <x:c r="G20" s="6" t="n">
+        <x:v>0.369</x:v>
+      </x:c>
+      <x:c r="H20" s="6" t="n">
+        <x:v>0.427</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="20" customHeight="1">
+      <x:c r="A21" s="5" t="str">
+        <x:v>ETTm2</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="C21" s="10" t="n">
+        <x:v>0.39</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="n">
+        <x:v>0.386</x:v>
+      </x:c>
+      <x:c r="E21" s="8" t="n">
+        <x:v>0.381</x:v>
+      </x:c>
+      <x:c r="F21" s="8" t="n">
+        <x:v>0.383</x:v>
+      </x:c>
+      <x:c r="G21" s="6" t="n">
+        <x:v>0.554</x:v>
+      </x:c>
+      <x:c r="H21" s="6" t="n">
+        <x:v>0.522</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="20" customHeight="1">
+      <x:c r="A22" s="5" t="str">
+        <x:v>ETTm2</x:v>
+      </x:c>
+      <x:c r="B22" s="4" t="str">
+        <x:v>AVG</x:v>
+      </x:c>
+      <x:c r="C22" s="10" t="n">
+        <x:v>0.27</x:v>
+      </x:c>
+      <x:c r="D22" s="8" t="n">
+        <x:v>0.312</x:v>
+      </x:c>
+      <x:c r="E22" s="8" t="n">
+        <x:v>0.266</x:v>
+      </x:c>
+      <x:c r="F22" s="10" t="n">
+        <x:v>0.313</x:v>
+      </x:c>
+      <x:c r="G22" s="6" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="H22" s="6" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="20" customHeight="1">
+      <x:c r="A23" s="5" t="str">
+        <x:v>ECL</x:v>
+      </x:c>
+      <x:c r="B23" s="4" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C23" s="8" t="n">
+        <x:v>0.13</x:v>
+      </x:c>
+      <x:c r="D23" s="8" t="n">
+        <x:v>0.219</x:v>
+      </x:c>
+      <x:c r="E23" s="10" t="n">
+        <x:v>0.159</x:v>
+      </x:c>
+      <x:c r="F23" s="10" t="n">
+        <x:v>0.244</x:v>
+      </x:c>
+      <x:c r="G23" s="6" t="n">
+        <x:v>0.197</x:v>
+      </x:c>
+      <x:c r="H23" s="6" t="n">
+        <x:v>0.282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="20" customHeight="1">
+      <x:c r="A24" s="5" t="str">
+        <x:v>ECL</x:v>
+      </x:c>
+      <x:c r="B24" s="4" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C24" s="8" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="D24" s="8" t="n">
+        <x:v>0.237</x:v>
+      </x:c>
+      <x:c r="E24" s="10" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="F24" s="10" t="n">
+        <x:v>0.248</x:v>
+      </x:c>
+      <x:c r="G24" s="6" t="n">
+        <x:v>0.196</x:v>
+      </x:c>
+      <x:c r="H24" s="6" t="n">
+        <x:v>0.285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="20" customHeight="1">
+      <x:c r="A25" s="5" t="str">
+        <x:v>ECL</x:v>
+      </x:c>
+      <x:c r="B25" s="4" t="n">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="C25" s="8" t="n">
+        <x:v>0.165</x:v>
+      </x:c>
+      <x:c r="D25" s="8" t="n">
+        <x:v>0.255</x:v>
+      </x:c>
+      <x:c r="E25" s="10" t="n">
+        <x:v>0.182</x:v>
+      </x:c>
+      <x:c r="F25" s="10" t="n">
+        <x:v>0.267</x:v>
+      </x:c>
+      <x:c r="G25" s="6" t="n">
+        <x:v>0.209</x:v>
+      </x:c>
+      <x:c r="H25" s="6" t="n">
+        <x:v>0.301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="20" customHeight="1">
+      <x:c r="A26" s="5" t="str">
+        <x:v>ECL</x:v>
+      </x:c>
+      <x:c r="B26" s="4" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="C26" s="8" t="n">
+        <x:v>0.187</x:v>
+      </x:c>
+      <x:c r="D26" s="8" t="n">
+        <x:v>0.274</x:v>
+      </x:c>
+      <x:c r="E26" s="10" t="n">
+        <x:v>0.216</x:v>
+      </x:c>
+      <x:c r="F26" s="10" t="n">
+        <x:v>0.298</x:v>
+      </x:c>
+      <x:c r="G26" s="6" t="n">
+        <x:v>0.245</x:v>
+      </x:c>
+      <x:c r="H26" s="6" t="n">
+        <x:v>0.333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="20" customHeight="1">
+      <x:c r="A27" s="5" t="str">
+        <x:v>ECL</x:v>
+      </x:c>
+      <x:c r="B27" s="4" t="str">
+        <x:v>AVG</x:v>
+      </x:c>
+      <x:c r="C27" s="8" t="n">
+        <x:v>0.158</x:v>
+      </x:c>
+      <x:c r="D27" s="8" t="n">
+        <x:v>0.246</x:v>
+      </x:c>
+      <x:c r="E27" s="10" t="n">
+        <x:v>0.179</x:v>
+      </x:c>
+      <x:c r="F27" s="10" t="n">
+        <x:v>0.264</x:v>
+      </x:c>
+      <x:c r="G27" s="6" t="n">
+        <x:v>0.211</x:v>
+      </x:c>
+      <x:c r="H27" s="6" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="20" customHeight="1">
+      <x:c r="A28" s="5" t="str">
+        <x:v>Weather</x:v>
+      </x:c>
+      <x:c r="B28" s="4" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C28" s="8" t="n">
+        <x:v>0.153</x:v>
+      </x:c>
+      <x:c r="D28" s="8" t="n">
+        <x:v>0.19</x:v>
+      </x:c>
+      <x:c r="E28" s="10" t="n">
+        <x:v>0.168</x:v>
+      </x:c>
+      <x:c r="F28" s="10" t="n">
+        <x:v>0.203</x:v>
+      </x:c>
+      <x:c r="G28" s="6" t="n">
+        <x:v>0.196</x:v>
+      </x:c>
+      <x:c r="H28" s="6" t="n">
+        <x:v>0.255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="20" customHeight="1">
+      <x:c r="A29" s="5" t="str">
+        <x:v>Weather</x:v>
+      </x:c>
+      <x:c r="B29" s="4" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C29" s="8" t="n">
+        <x:v>0.204</x:v>
+      </x:c>
+      <x:c r="D29" s="8" t="n">
+        <x:v>0.239</x:v>
+      </x:c>
+      <x:c r="E29" s="10" t="n">
+        <x:v>0.214</x:v>
+      </x:c>
+      <x:c r="F29" s="10" t="n">
+        <x:v>0.245</x:v>
+      </x:c>
+      <x:c r="G29" s="6" t="n">
+        <x:v>0.237</x:v>
+      </x:c>
+      <x:c r="H29" s="6" t="n">
+        <x:v>0.296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="20" customHeight="1">
+      <x:c r="A30" s="5" t="str">
+        <x:v>Weather</x:v>
+      </x:c>
+      <x:c r="B30" s="4" t="n">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="n">
+        <x:v>0.261</x:v>
+      </x:c>
+      <x:c r="D30" s="10" t="n">
+        <x:v>0.282</x:v>
+      </x:c>
+      <x:c r="E30" s="8" t="n">
+        <x:v>0.236</x:v>
+      </x:c>
+      <x:c r="F30" s="8" t="n">
+        <x:v>0.273</x:v>
+      </x:c>
+      <x:c r="G30" s="6" t="n">
+        <x:v>0.283</x:v>
+      </x:c>
+      <x:c r="H30" s="6" t="n">
+        <x:v>0.335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="20" customHeight="1">
+      <x:c r="A31" s="5" t="str">
+        <x:v>Weather</x:v>
+      </x:c>
+      <x:c r="B31" s="4" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="C31" s="10" t="n">
+        <x:v>0.342</x:v>
+      </x:c>
+      <x:c r="D31" s="10" t="n">
+        <x:v>0.336</x:v>
+      </x:c>
+      <x:c r="E31" s="8" t="n">
+        <x:v>0.309</x:v>
+      </x:c>
+      <x:c r="F31" s="8" t="n">
+        <x:v>0.321</x:v>
+      </x:c>
+      <x:c r="G31" s="6" t="n">
+        <x:v>0.345</x:v>
+      </x:c>
+      <x:c r="H31" s="6" t="n">
+        <x:v>0.381</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="20" customHeight="1">
+      <x:c r="A32" s="5" t="str">
+        <x:v>Weather</x:v>
+      </x:c>
+      <x:c r="B32" s="4" t="str">
+        <x:v>AVG</x:v>
+      </x:c>
+      <x:c r="C32" s="10" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="D32" s="10" t="n">
+        <x:v>0.261</x:v>
+      </x:c>
+      <x:c r="E32" s="8" t="n">
+        <x:v>0.231</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="n">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="G32" s="6" t="n">
+        <x:v>0.265</x:v>
+      </x:c>
+      <x:c r="H32" s="6" t="n">
+        <x:v>0.316</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="20" customHeight="1">
+      <x:c r="A33" s="5" t="str">
+        <x:v>Solar</x:v>
+      </x:c>
+      <x:c r="B33" s="4" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C33" s="8" t="n">
+        <x:v>0.168</x:v>
+      </x:c>
+      <x:c r="D33" s="8" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="E33" s="10" t="n">
+        <x:v>0.201</x:v>
+      </x:c>
+      <x:c r="F33" s="10" t="n">
+        <x:v>0.215</x:v>
+      </x:c>
+      <x:c r="G33" s="6" t="n">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="H33" s="6" t="n">
+        <x:v>0.378</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="20" customHeight="1">
+      <x:c r="A34" s="5" t="str">
+        <x:v>Solar</x:v>
+      </x:c>
+      <x:c r="B34" s="4" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C34" s="8" t="n">
+        <x:v>0.19</x:v>
+      </x:c>
+      <x:c r="D34" s="8" t="n">
+        <x:v>0.22</x:v>
+      </x:c>
+      <x:c r="E34" s="10" t="n">
+        <x:v>0.235</x:v>
+      </x:c>
+      <x:c r="F34" s="10" t="n">
+        <x:v>0.234</x:v>
+      </x:c>
+      <x:c r="G34" s="6" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="H34" s="6" t="n">
+        <x:v>0.398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="20" customHeight="1">
+      <x:c r="A35" s="5" t="str">
+        <x:v>Solar</x:v>
+      </x:c>
+      <x:c r="B35" s="4" t="n">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="C35" s="8" t="n">
+        <x:v>0.224</x:v>
+      </x:c>
+      <x:c r="D35" s="8" t="n">
+        <x:v>0.231</x:v>
+      </x:c>
+      <x:c r="E35" s="10" t="n">
+        <x:v>0.258</x:v>
+      </x:c>
+      <x:c r="F35" s="10" t="n">
+        <x:v>0.249</x:v>
+      </x:c>
+      <x:c r="G35" s="6" t="n">
+        <x:v>0.353</x:v>
+      </x:c>
+      <x:c r="H35" s="6" t="n">
+        <x:v>0.415</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="20" customHeight="1">
+      <x:c r="A36" s="5" t="str">
+        <x:v>Solar</x:v>
+      </x:c>
+      <x:c r="B36" s="4" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="C36" s="8" t="n">
+        <x:v>0.208</x:v>
+      </x:c>
+      <x:c r="D36" s="8" t="n">
+        <x:v>0.243</x:v>
+      </x:c>
+      <x:c r="E36" s="10" t="n">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="F36" s="10" t="n">
+        <x:v>0.247</x:v>
+      </x:c>
+      <x:c r="G36" s="6" t="n">
+        <x:v>0.356</x:v>
+      </x:c>
+      <x:c r="H36" s="6" t="n">
+        <x:v>0.413</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="20" customHeight="1">
+      <x:c r="A37" s="5" t="str">
+        <x:v>Solar</x:v>
+      </x:c>
+      <x:c r="B37" s="4" t="str">
+        <x:v>AVG</x:v>
+      </x:c>
+      <x:c r="C37" s="8" t="n">
+        <x:v>0.197</x:v>
+      </x:c>
+      <x:c r="D37" s="8" t="n">
+        <x:v>0.223</x:v>
+      </x:c>
+      <x:c r="E37" s="10" t="n">
+        <x:v>0.238</x:v>
+      </x:c>
+      <x:c r="F37" s="10" t="n">
+        <x:v>0.236</x:v>
+      </x:c>
+      <x:c r="G37" s="6" t="n">
+        <x:v>0.329</x:v>
+      </x:c>
+      <x:c r="H37" s="6" t="n">
+        <x:v>0.401</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="20" customHeight="1">
+      <x:c r="A38" s="5" t="str">
+        <x:v>Exchange</x:v>
+      </x:c>
+      <x:c r="B38" s="4" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C38" s="10" t="n">
+        <x:v>0.083</x:v>
+      </x:c>
+      <x:c r="D38" s="10" t="n">
+        <x:v>0.202</x:v>
+      </x:c>
+      <x:c r="E38" s="8" t="n">
+        <x:v>0.082</x:v>
+      </x:c>
+      <x:c r="F38" s="8" t="n">
+        <x:v>0.199</x:v>
+      </x:c>
+      <x:c r="G38" s="6" t="n">
+        <x:v>0.088</x:v>
+      </x:c>
+      <x:c r="H38" s="6" t="n">
+        <x:v>0.218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="20" customHeight="1">
+      <x:c r="A39" s="5" t="str">
+        <x:v>Exchange</x:v>
+      </x:c>
+      <x:c r="B39" s="4" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C39" s="8" t="n">
+        <x:v>0.176</x:v>
+      </x:c>
+      <x:c r="D39" s="10" t="n">
+        <x:v>0.299</x:v>
+      </x:c>
+      <x:c r="E39" s="10" t="n">
+        <x:v>0.177</x:v>
+      </x:c>
+      <x:c r="F39" s="8" t="n">
+        <x:v>0.298</x:v>
+      </x:c>
+      <x:c r="G39" s="8" t="n">
+        <x:v>0.176</x:v>
+      </x:c>
+      <x:c r="H39" s="6" t="n">
+        <x:v>0.315</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="20" customHeight="1">
+      <x:c r="A40" s="5" t="str">
+        <x:v>Exchange</x:v>
+      </x:c>
+      <x:c r="B40" s="4" t="n">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="C40" s="10" t="n">
+        <x:v>0.334</x:v>
+      </x:c>
+      <x:c r="D40" s="8" t="n">
+        <x:v>0.417</x:v>
+      </x:c>
+      <x:c r="E40" s="6" t="n">
+        <x:v>0.349</x:v>
+      </x:c>
+      <x:c r="F40" s="10" t="n">
+        <x:v>0.425</x:v>
+      </x:c>
+      <x:c r="G40" s="8" t="n">
+        <x:v>0.313</x:v>
+      </x:c>
+      <x:c r="H40" s="6" t="n">
+        <x:v>0.427</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="20" customHeight="1">
+      <x:c r="A41" s="5" t="str">
+        <x:v>Exchange</x:v>
+      </x:c>
+      <x:c r="B41" s="4" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="C41" s="8" t="n">
+        <x:v>0.827</x:v>
+      </x:c>
+      <x:c r="D41" s="8" t="n">
+        <x:v>0.688</x:v>
+      </x:c>
+      <x:c r="E41" s="6" t="n">
+        <x:v>0.891</x:v>
+      </x:c>
+      <x:c r="F41" s="6" t="n">
+        <x:v>0.711</x:v>
+      </x:c>
+      <x:c r="G41" s="10" t="n">
+        <x:v>0.839</x:v>
+      </x:c>
+      <x:c r="H41" s="10" t="n">
+        <x:v>0.695</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="20" customHeight="1">
+      <x:c r="A42" s="5" t="str">
+        <x:v>Exchange</x:v>
+      </x:c>
+      <x:c r="B42" s="4" t="str">
+        <x:v>AVG</x:v>
+      </x:c>
+      <x:c r="C42" s="10" t="n">
+        <x:v>0.355</x:v>
+      </x:c>
+      <x:c r="D42" s="8" t="n">
+        <x:v>0.401</x:v>
+      </x:c>
+      <x:c r="E42" s="6" t="n">
+        <x:v>0.374</x:v>
+      </x:c>
+      <x:c r="F42" s="10" t="n">
+        <x:v>0.408</x:v>
+      </x:c>
+      <x:c r="G42" s="8" t="n">
+        <x:v>0.354</x:v>
+      </x:c>
+      <x:c r="H42" s="6" t="n">
+        <x:v>0.413</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="20" customHeight="1">
+      <x:c r="A43" s="5" t="str">
+        <x:v>Traffic</x:v>
+      </x:c>
+      <x:c r="B43" s="4" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C43" s="8" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D43" s="8" t="n">
+        <x:v>0.237</x:v>
+      </x:c>
+      <x:c r="E43" s="10" t="n">
+        <x:v>0.471</x:v>
+      </x:c>
+      <x:c r="F43" s="10" t="n">
+        <x:v>0.275</x:v>
+      </x:c>
+      <x:c r="G43" s="6" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H43" s="6" t="n">
+        <x:v>0.396</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="20" customHeight="1">
+      <x:c r="A44" s="5" t="str">
+        <x:v>Traffic</x:v>
+      </x:c>
+      <x:c r="B44" s="4" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C44" s="8" t="n">
+        <x:v>0.418</x:v>
+      </x:c>
+      <x:c r="D44" s="8" t="n">
+        <x:v>0.249</x:v>
+      </x:c>
+      <x:c r="E44" s="10" t="n">
+        <x:v>0.478</x:v>
+      </x:c>
+      <x:c r="F44" s="10" t="n">
+        <x:v>0.272</x:v>
+      </x:c>
+      <x:c r="G44" s="6" t="n">
+        <x:v>0.598</x:v>
+      </x:c>
+      <x:c r="H44" s="6" t="n">
+        <x:v>0.37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="20" customHeight="1">
+      <x:c r="A45" s="5" t="str">
+        <x:v>Traffic</x:v>
+      </x:c>
+      <x:c r="B45" s="4" t="n">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="C45" s="8" t="n">
+        <x:v>0.438</x:v>
+      </x:c>
+      <x:c r="D45" s="8" t="n">
+        <x:v>0.256</x:v>
+      </x:c>
+      <x:c r="E45" s="10" t="n">
+        <x:v>0.501</x:v>
+      </x:c>
+      <x:c r="F45" s="10" t="n">
+        <x:v>0.276</x:v>
+      </x:c>
+      <x:c r="G45" s="6" t="n">
+        <x:v>0.605</x:v>
+      </x:c>
+      <x:c r="H45" s="6" t="n">
+        <x:v>0.373</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="20" customHeight="1">
+      <x:c r="A46" s="5" t="str">
+        <x:v>Traffic</x:v>
+      </x:c>
+      <x:c r="B46" s="4" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="C46" s="8" t="n">
+        <x:v>0.47</x:v>
+      </x:c>
+      <x:c r="D46" s="8" t="n">
+        <x:v>0.275</x:v>
+      </x:c>
+      <x:c r="E46" s="10" t="n">
+        <x:v>0.547</x:v>
+      </x:c>
+      <x:c r="F46" s="10" t="n">
+        <x:v>0.291</x:v>
+      </x:c>
+      <x:c r="G46" s="6" t="n">
+        <x:v>0.645</x:v>
+      </x:c>
+      <x:c r="H46" s="6" t="n">
+        <x:v>0.394</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="20" customHeight="1">
+      <x:c r="A47" s="5" t="str">
+        <x:v>Traffic</x:v>
+      </x:c>
+      <x:c r="B47" s="4" t="str">
+        <x:v>AVG</x:v>
+      </x:c>
+      <x:c r="C47" s="8" t="n">
+        <x:v>0.431</x:v>
+      </x:c>
+      <x:c r="D47" s="8" t="n">
+        <x:v>0.254</x:v>
+      </x:c>
+      <x:c r="E47" s="10" t="n">
+        <x:v>0.499</x:v>
+      </x:c>
+      <x:c r="F47" s="10" t="n">
+        <x:v>0.278</x:v>
+      </x:c>
+      <x:c r="G47" s="6" t="n">
+        <x:v>0.624</x:v>
+      </x:c>
+      <x:c r="H47" s="6" t="n">
+        <x:v>0.383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="20" customHeight="1">
+      <x:c r="A48" s="7" t="str">
+        <x:v>1 count</x:v>
+      </x:c>
+      <x:c r="B48" s="7"/>
+      <x:c r="C48" s="7" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D48" s="7"/>
+      <x:c r="E48" s="7" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F48" s="7"/>
+      <x:c r="G48" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H48" s="7"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:A2"/>
+    <x:mergeCell ref="B1:B2"/>
+    <x:mergeCell ref="C1:D1"/>
+    <x:mergeCell ref="E1:F1"/>
+    <x:mergeCell ref="G1:H1"/>
+    <x:mergeCell ref="A3:A7"/>
+    <x:mergeCell ref="A8:A12"/>
+    <x:mergeCell ref="A13:A17"/>
+    <x:mergeCell ref="A18:A22"/>
+    <x:mergeCell ref="A23:A27"/>
+    <x:mergeCell ref="A28:A32"/>
+    <x:mergeCell ref="A33:A37"/>
+    <x:mergeCell ref="A38:A42"/>
+    <x:mergeCell ref="A43:A47"/>
+    <x:mergeCell ref="A48:B48"/>
+    <x:mergeCell ref="C48:D48"/>
+    <x:mergeCell ref="E48:F48"/>
+    <x:mergeCell ref="G48:H48"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
